--- a/Data/National Accounts/PSA-11ESWW_2018PSNA_Qrt.xlsx
+++ b/Data/National Accounts/PSA-11ESWW_2018PSNA_Qrt.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\Shared drives\QNAP\NAP Dissemination\As of January 2026\Tables\Prelim Q4 2025\NAP Q1 2000 to Q4 2025\Qtr\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="I:\Shared drives\QNAP\NAP Dissemination\As of April 2026\Tables\NAP Q1 2000 to Q4 2025\Qtr\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBAB222F-19B4-481A-BCAC-A4608882E72B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90E28C18-FBDF-4086-90A2-5626A8499ABE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="794" xr2:uid="{736930C2-BFBB-46C3-AE9E-AECFC8C3145D}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="794" xr2:uid="{736930C2-BFBB-46C3-AE9E-AECFC8C3145D}"/>
   </bookViews>
   <sheets>
     <sheet name="ESWW" sheetId="11" r:id="rId1"/>
@@ -693,10 +693,10 @@
     <t>Table 12.7 Gross Value Added in Electricity, Steam, Water and Waste Management, by Industry</t>
   </si>
   <si>
-    <t>As of January 2026</t>
+    <t>Q1 2000 to Q4 2025</t>
   </si>
   <si>
-    <t>Q1 2000 to Q4 2025</t>
+    <t>As of April 2026</t>
   </si>
 </sst>
 </file>
@@ -744,10 +744,12 @@
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="12"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="12"/>
@@ -1215,7 +1217,7 @@
     </row>
     <row r="3" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="5" spans="1:179" x14ac:dyDescent="0.2">
@@ -1225,7 +1227,7 @@
     </row>
     <row r="6" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="7" spans="1:179" x14ac:dyDescent="0.2">
@@ -2014,19 +2016,19 @@
         <v>151189.41872020048</v>
       </c>
       <c r="CW12" s="21">
-        <v>147255.33193057618</v>
+        <v>147681.10153236226</v>
       </c>
       <c r="CX12" s="21">
-        <v>192637.59503296064</v>
+        <v>192634.15193816851</v>
       </c>
       <c r="CY12" s="21">
         <v>258206.34370975947</v>
       </c>
       <c r="CZ12" s="21">
-        <v>151072.49973241842</v>
+        <v>151033.74107909951</v>
       </c>
       <c r="DA12" s="21">
-        <v>147196.18229663512</v>
+        <v>151678.73447707252</v>
       </c>
       <c r="DB12" s="11"/>
       <c r="DC12" s="11"/>
@@ -2417,7 +2419,7 @@
         <v>2450.2353867769821</v>
       </c>
       <c r="DA13" s="21">
-        <v>3132.9803484120248</v>
+        <v>3133.9499880779931</v>
       </c>
       <c r="DB13" s="11"/>
       <c r="DC13" s="11"/>
@@ -2796,19 +2798,19 @@
         <v>30614.881767554161</v>
       </c>
       <c r="CW14" s="21">
-        <v>36621.250776370951</v>
+        <v>36609.697381313759</v>
       </c>
       <c r="CX14" s="21">
-        <v>37923.45497722859</v>
+        <v>37927.965669851576</v>
       </c>
       <c r="CY14" s="21">
-        <v>40596.500708737025</v>
+        <v>40544.66235376976</v>
       </c>
       <c r="CZ14" s="21">
-        <v>33019.217802486804</v>
+        <v>33019.681634820918</v>
       </c>
       <c r="DA14" s="21">
-        <v>39530.475825214526</v>
+        <v>40051.882566551401</v>
       </c>
       <c r="DB14" s="11"/>
       <c r="DC14" s="11"/>
@@ -3187,19 +3189,19 @@
         <v>2766.544466466391</v>
       </c>
       <c r="CW15" s="21">
-        <v>3436.2763991786846</v>
+        <v>3367.0727543114945</v>
       </c>
       <c r="CX15" s="21">
-        <v>2845.5078765960234</v>
+        <v>2858.8573484974554</v>
       </c>
       <c r="CY15" s="21">
-        <v>2908.1660062595647</v>
+        <v>2917.2337135595612</v>
       </c>
       <c r="CZ15" s="21">
         <v>3095.4875623642383</v>
       </c>
       <c r="DA15" s="21">
-        <v>3553.3126404144341</v>
+        <v>3608.4485562785258</v>
       </c>
       <c r="DB15" s="11"/>
       <c r="DC15" s="11"/>
@@ -3758,19 +3760,19 @@
         <v>187319.98532841628</v>
       </c>
       <c r="CW17" s="23">
-        <v>190882.6785317972</v>
+        <v>191227.69109365885</v>
       </c>
       <c r="CX17" s="23">
-        <v>237948.11523396568</v>
+        <v>237962.53230369795</v>
       </c>
       <c r="CY17" s="23">
-        <v>305653.73974186729</v>
+        <v>305610.96909420006</v>
       </c>
       <c r="CZ17" s="23">
-        <v>189637.44048404644</v>
+        <v>189599.14566306162</v>
       </c>
       <c r="DA17" s="23">
-        <v>193412.95111067611</v>
+        <v>198473.01558798042</v>
       </c>
       <c r="DB17" s="11"/>
       <c r="DC17" s="11"/>
@@ -4331,7 +4333,7 @@
     </row>
     <row r="24" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A24" s="6" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="26" spans="1:179" x14ac:dyDescent="0.2">
@@ -4341,7 +4343,7 @@
     </row>
     <row r="27" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A27" s="6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="28" spans="1:179" x14ac:dyDescent="0.2">
@@ -5130,19 +5132,19 @@
         <v>173687.01380465535</v>
       </c>
       <c r="CW33" s="21">
-        <v>139929.01591262216</v>
+        <v>140333.66623955645</v>
       </c>
       <c r="CX33" s="21">
-        <v>135272.21010767654</v>
+        <v>135269.78216409852</v>
       </c>
       <c r="CY33" s="21">
         <v>153987.27406579338</v>
       </c>
       <c r="CZ33" s="21">
-        <v>171751.59111216696</v>
+        <v>171707.52710059189</v>
       </c>
       <c r="DA33" s="21">
-        <v>136388.0919187924</v>
+        <v>140543.05758884398</v>
       </c>
       <c r="DB33" s="11"/>
       <c r="DC33" s="11"/>
@@ -5533,7 +5535,7 @@
         <v>2317.0602068468729</v>
       </c>
       <c r="DA34" s="21">
-        <v>3045.9215505912721</v>
+        <v>3045.9215505912725</v>
       </c>
       <c r="DB34" s="11"/>
       <c r="DC34" s="11"/>
@@ -5912,19 +5914,19 @@
         <v>25893.994705329045</v>
       </c>
       <c r="CW35" s="21">
-        <v>30333.587733344346</v>
+        <v>30324.017769339753</v>
       </c>
       <c r="CX35" s="21">
-        <v>29159.613662520165</v>
+        <v>29163.081966088917</v>
       </c>
       <c r="CY35" s="21">
-        <v>29642.180104690306</v>
+        <v>29603.79571592309</v>
       </c>
       <c r="CZ35" s="21">
-        <v>26512.635276772184</v>
+        <v>26513.007708898753</v>
       </c>
       <c r="DA35" s="21">
-        <v>31001.475489679804</v>
+        <v>31410.384537318914</v>
       </c>
       <c r="DB35" s="11"/>
       <c r="DC35" s="11"/>
@@ -6303,19 +6305,19 @@
         <v>2318.9014023446825</v>
       </c>
       <c r="CW36" s="21">
-        <v>2929.6907052887482</v>
+        <v>2870.6473338471596</v>
       </c>
       <c r="CX36" s="21">
-        <v>2379.889862681996</v>
+        <v>2391.0549250287504</v>
       </c>
       <c r="CY36" s="21">
-        <v>2389.1432530199895</v>
+        <v>2396.5926392206111</v>
       </c>
       <c r="CZ36" s="21">
         <v>2569.2041215764948</v>
       </c>
       <c r="DA36" s="21">
-        <v>3001.5729619763024</v>
+        <v>3048.1809276549402</v>
       </c>
       <c r="DB36" s="11"/>
       <c r="DC36" s="11"/>
@@ -6874,19 +6876,19 @@
         <v>204412.16907001744</v>
       </c>
       <c r="CW38" s="23">
-        <v>176341.16246970327</v>
+        <v>176677.19946119137</v>
       </c>
       <c r="CX38" s="23">
-        <v>170272.79738315119</v>
+        <v>170285.00280548868</v>
       </c>
       <c r="CY38" s="23">
-        <v>189381.86159368602</v>
+        <v>189350.92659111944</v>
       </c>
       <c r="CZ38" s="23">
-        <v>203150.49071736255</v>
+        <v>203106.79913791403</v>
       </c>
       <c r="DA38" s="23">
-        <v>173437.0619210398</v>
+        <v>178047.54460440911</v>
       </c>
       <c r="DB38" s="11"/>
       <c r="DC38" s="11"/>
@@ -7447,7 +7449,7 @@
     </row>
     <row r="45" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A45" s="6" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="47" spans="1:179" x14ac:dyDescent="0.2">
@@ -7464,7 +7466,7 @@
     </row>
     <row r="48" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A48" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="CY48" s="9"/>
       <c r="CZ48" s="9"/>
@@ -8248,19 +8250,19 @@
         <v>7.3036775132127474</v>
       </c>
       <c r="CS54" s="16">
-        <v>5.4066071268651399</v>
+        <v>5.7113765946572101</v>
       </c>
       <c r="CT54" s="16">
-        <v>3.4482218234287672</v>
+        <v>3.4463728487581875</v>
       </c>
       <c r="CU54" s="16">
         <v>4.2285476707859715</v>
       </c>
       <c r="CV54" s="16">
-        <v>-7.7332784775393293E-2</v>
+        <v>-0.10296860879469705</v>
       </c>
       <c r="CW54" s="16">
-        <v>-4.0168076201780423E-2</v>
+        <v>2.7069360285305351</v>
       </c>
       <c r="CX54" s="18"/>
       <c r="CY54" s="18"/>
@@ -8639,7 +8641,7 @@
         <v>-10.872670971040293</v>
       </c>
       <c r="CW55" s="16">
-        <v>-12.237007679377811</v>
+        <v>-12.209845530530856</v>
       </c>
       <c r="CX55" s="18"/>
       <c r="CY55" s="18"/>
@@ -9006,19 +9008,19 @@
         <v>15.467018450722918</v>
       </c>
       <c r="CS56" s="16">
-        <v>12.275140934743618</v>
+        <v>12.239719996604663</v>
       </c>
       <c r="CT56" s="16">
-        <v>9.6046416336907185</v>
+        <v>9.6176782319848257</v>
       </c>
       <c r="CU56" s="16">
-        <v>8.6408413617061797</v>
+        <v>8.5021160430178497</v>
       </c>
       <c r="CV56" s="16">
-        <v>7.8534878990804202</v>
+        <v>7.8550029542017654</v>
       </c>
       <c r="CW56" s="16">
-        <v>7.944089803510181</v>
+        <v>9.4023863387480304</v>
       </c>
       <c r="CX56" s="18"/>
       <c r="CY56" s="18"/>
@@ -9385,19 +9387,19 @@
         <v>5.0111682722761657</v>
       </c>
       <c r="CS57" s="16">
-        <v>15.374624483446524</v>
+        <v>13.051078990614172</v>
       </c>
       <c r="CT57" s="16">
-        <v>3.3314474544643815</v>
+        <v>3.8162186496781629</v>
       </c>
       <c r="CU57" s="16">
-        <v>13.495414700247935</v>
+        <v>13.84929518649885</v>
       </c>
       <c r="CV57" s="16">
         <v>11.890034658217317</v>
       </c>
       <c r="CW57" s="16">
-        <v>3.4059030077942225</v>
+        <v>7.1687135853525206</v>
       </c>
       <c r="CX57" s="18"/>
       <c r="CY57" s="18"/>
@@ -9940,19 +9942,19 @@
         <v>8.3000649088542389</v>
       </c>
       <c r="CS59" s="16">
-        <v>6.8147327594068514</v>
+        <v>7.007795979586632</v>
       </c>
       <c r="CT59" s="16">
-        <v>4.5399746349715286</v>
+        <v>4.5463086212804313</v>
       </c>
       <c r="CU59" s="16">
-        <v>4.9521081750127678</v>
+        <v>4.9374220480101059</v>
       </c>
       <c r="CV59" s="16">
-        <v>1.2371638571117245</v>
+        <v>1.216720325196178</v>
       </c>
       <c r="CW59" s="16">
-        <v>1.3255642671932861</v>
+        <v>3.7888469252985999</v>
       </c>
       <c r="CX59" s="18"/>
       <c r="CY59" s="18"/>
@@ -10517,7 +10519,7 @@
     </row>
     <row r="66" spans="1:175" x14ac:dyDescent="0.2">
       <c r="A66" s="6" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="CX66" s="7"/>
       <c r="CY66" s="7"/>
@@ -10541,7 +10543,7 @@
     </row>
     <row r="69" spans="1:175" x14ac:dyDescent="0.2">
       <c r="A69" s="6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="CX69" s="7"/>
       <c r="CY69" s="7"/>
@@ -11326,19 +11328,19 @@
         <v>7.30367751321279</v>
       </c>
       <c r="CS75" s="16">
-        <v>5.5597698806095082</v>
+        <v>5.8650303379543374</v>
       </c>
       <c r="CT75" s="16">
-        <v>2.3657307629235476</v>
+        <v>2.363893443799256</v>
       </c>
       <c r="CU75" s="16">
         <v>-4.2321041547694449E-2</v>
       </c>
       <c r="CV75" s="16">
-        <v>-1.1143162923309546</v>
+        <v>-1.1396860713431209</v>
       </c>
       <c r="CW75" s="16">
-        <v>-2.530514468879602</v>
+        <v>0.14920963365277373</v>
       </c>
       <c r="CX75" s="18"/>
       <c r="CY75" s="18"/>
@@ -12084,19 +12086,19 @@
         <v>7.6573601354296414</v>
       </c>
       <c r="CS77" s="16">
-        <v>5.0487799777198035</v>
+        <v>5.0156380674403209</v>
       </c>
       <c r="CT77" s="16">
-        <v>3.4355767461810842</v>
+        <v>3.4478795833900051</v>
       </c>
       <c r="CU77" s="16">
-        <v>2.6110575973115431</v>
+        <v>2.4781840126858725</v>
       </c>
       <c r="CV77" s="16">
-        <v>2.3891275891696324</v>
+        <v>2.3905658845381481</v>
       </c>
       <c r="CW77" s="16">
-        <v>2.2018093019747766</v>
+        <v>3.5825291234249761</v>
       </c>
       <c r="CX77" s="18"/>
       <c r="CY77" s="18"/>
@@ -12463,19 +12465,19 @@
         <v>2.8724479408652712</v>
       </c>
       <c r="CS78" s="16">
-        <v>13.599114873219236</v>
+        <v>11.30970093515846</v>
       </c>
       <c r="CT78" s="16">
-        <v>2.0734993984969918</v>
+        <v>2.5523690313342513</v>
       </c>
       <c r="CU78" s="16">
-        <v>12.379174000274375</v>
+        <v>12.72957403048467</v>
       </c>
       <c r="CV78" s="16">
         <v>10.794021642262436</v>
       </c>
       <c r="CW78" s="16">
-        <v>2.4535783438774104</v>
+        <v>6.184444592497357</v>
       </c>
       <c r="CX78" s="18"/>
       <c r="CY78" s="18"/>
@@ -13018,19 +13020,19 @@
         <v>7.1468243714466411</v>
       </c>
       <c r="CS80" s="16">
-        <v>5.6728884030393658</v>
+        <v>5.874259421600712</v>
       </c>
       <c r="CT80" s="16">
-        <v>2.6946440852568116</v>
+        <v>2.7020053991138866</v>
       </c>
       <c r="CU80" s="16">
-        <v>0.73579560083705076</v>
+        <v>0.71934068763030723</v>
       </c>
       <c r="CV80" s="16">
-        <v>-0.61722272132571732</v>
+        <v>-0.63859697690320161</v>
       </c>
       <c r="CW80" s="16">
-        <v>-1.6468648090955043</v>
+        <v>0.77562082000216037</v>
       </c>
       <c r="CX80" s="18"/>
       <c r="CY80" s="18"/>
@@ -13582,7 +13584,7 @@
     </row>
     <row r="86" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A86" s="6" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="88" spans="1:179" x14ac:dyDescent="0.2">
@@ -13592,7 +13594,7 @@
     </row>
     <row r="89" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A89" s="6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="90" spans="1:179" x14ac:dyDescent="0.2">
@@ -14381,19 +14383,19 @@
         <v>87.047048255572079</v>
       </c>
       <c r="CW95" s="16">
-        <v>105.2357375417611</v>
+        <v>105.23568968850523</v>
       </c>
       <c r="CX95" s="16">
-        <v>142.40736872682226</v>
+        <v>142.4073794282304</v>
       </c>
       <c r="CY95" s="16">
         <v>167.6803133741019</v>
       </c>
       <c r="CZ95" s="16">
-        <v>87.959883663468645</v>
+        <v>87.959883663468631</v>
       </c>
       <c r="DA95" s="16">
-        <v>107.92451175596622</v>
+        <v>107.92332049641738</v>
       </c>
       <c r="DB95" s="11"/>
       <c r="DC95" s="11"/>
@@ -14784,7 +14786,7 @@
         <v>105.74759255441784</v>
       </c>
       <c r="DA96" s="16">
-        <v>102.85820880067817</v>
+        <v>102.89004283349428</v>
       </c>
       <c r="DB96" s="11"/>
       <c r="DC96" s="11"/>
@@ -15163,19 +15165,19 @@
         <v>118.23159043611587</v>
       </c>
       <c r="CW97" s="16">
-        <v>120.72838563739975</v>
+        <v>120.72838652116008</v>
       </c>
       <c r="CX97" s="16">
-        <v>130.05472368782748</v>
+        <v>130.05472368782745</v>
       </c>
       <c r="CY97" s="16">
-        <v>136.95517861830078</v>
+        <v>136.95764807606031</v>
       </c>
       <c r="CZ97" s="16">
-        <v>124.5414401766959</v>
+        <v>124.54144017669593</v>
       </c>
       <c r="DA97" s="16">
-        <v>127.51159485416741</v>
+        <v>127.51159578758246</v>
       </c>
       <c r="DB97" s="11"/>
       <c r="DC97" s="11"/>
@@ -15554,10 +15556,10 @@
         <v>119.30410079829564</v>
       </c>
       <c r="CW98" s="16">
-        <v>117.29143943336528</v>
+        <v>117.29315247509138</v>
       </c>
       <c r="CX98" s="16">
-        <v>119.56468747630629</v>
+        <v>119.5646874763063</v>
       </c>
       <c r="CY98" s="16">
         <v>121.72422070478636</v>
@@ -15566,7 +15568,7 @@
         <v>120.48429847858135</v>
       </c>
       <c r="DA98" s="16">
-        <v>118.38168471756403</v>
+        <v>118.38039282840789</v>
       </c>
       <c r="DB98" s="11"/>
       <c r="DC98" s="11"/>
@@ -16125,19 +16127,19 @@
         <v>91.638372696027432</v>
       </c>
       <c r="CW100" s="16">
-        <v>108.24624033234002</v>
+        <v>108.23563633385733</v>
       </c>
       <c r="CX100" s="16">
-        <v>139.74523170517378</v>
+        <v>139.74368170021128</v>
       </c>
       <c r="CY100" s="16">
-        <v>161.39546689938007</v>
+        <v>161.39924667711304</v>
       </c>
       <c r="CZ100" s="16">
-        <v>93.34825616930631</v>
+        <v>93.349482374698638</v>
       </c>
       <c r="DA100" s="16">
-        <v>111.51765889503518</v>
+        <v>111.47191949709455</v>
       </c>
       <c r="DB100" s="11"/>
       <c r="DC100" s="11"/>
@@ -16338,7 +16340,7 @@
     </row>
     <row r="107" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A107" s="6" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="109" spans="1:179" x14ac:dyDescent="0.2">
@@ -16348,7 +16350,7 @@
     </row>
     <row r="110" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A110" s="6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="111" spans="1:179" x14ac:dyDescent="0.2">
@@ -17137,19 +17139,19 @@
         <v>80.711846338835457</v>
       </c>
       <c r="CW116" s="16">
-        <v>77.144418269490288</v>
+        <v>77.227885087014684</v>
       </c>
       <c r="CX116" s="16">
-        <v>80.95781504448864</v>
+        <v>80.951463271671926</v>
       </c>
       <c r="CY116" s="16">
-        <v>84.476749385700828</v>
+        <v>84.488572015283651</v>
       </c>
       <c r="CZ116" s="16">
-        <v>79.663857172301192</v>
+        <v>79.6595050842175</v>
       </c>
       <c r="DA116" s="16">
-        <v>76.104615255265657</v>
+        <v>76.422849739911044</v>
       </c>
       <c r="DB116" s="11"/>
       <c r="DC116" s="11"/>
@@ -17528,19 +17530,19 @@
         <v>1.4676172269474419</v>
       </c>
       <c r="CW117" s="16">
-        <v>1.8701641516816252</v>
+        <v>1.8667900058067084</v>
       </c>
       <c r="CX117" s="16">
-        <v>1.9086334610025604</v>
+        <v>1.90851782556435</v>
       </c>
       <c r="CY117" s="16">
-        <v>1.2899332821646503</v>
+        <v>1.2901138099843461</v>
       </c>
       <c r="CZ117" s="16">
-        <v>1.2920630970987568</v>
+        <v>1.2923240651787102</v>
       </c>
       <c r="DA117" s="16">
-        <v>1.6198400005898512</v>
+        <v>1.5790307709053553</v>
       </c>
       <c r="DB117" s="11"/>
       <c r="DC117" s="11"/>
@@ -17919,19 +17921,19 @@
         <v>16.34362810453942</v>
       </c>
       <c r="CW118" s="16">
-        <v>19.185214215375016</v>
+        <v>19.144558600241211</v>
       </c>
       <c r="CX118" s="16">
-        <v>15.937699250082247</v>
+        <v>15.938629204637259</v>
       </c>
       <c r="CY118" s="16">
-        <v>13.28185964386428</v>
+        <v>13.266756253527165</v>
       </c>
       <c r="CZ118" s="16">
-        <v>17.411760946681095</v>
+        <v>17.415522374505048</v>
       </c>
       <c r="DA118" s="16">
-        <v>20.438380986490465</v>
+        <v>20.180014118240138</v>
       </c>
       <c r="DB118" s="11"/>
       <c r="DC118" s="11"/>
@@ -18310,19 +18312,19 @@
         <v>1.4769083296776815</v>
       </c>
       <c r="CW119" s="16">
-        <v>1.8002033634530492</v>
+        <v>1.7607663069374095</v>
       </c>
       <c r="CX119" s="16">
-        <v>1.1958522444265378</v>
+        <v>1.2013896981264511</v>
       </c>
       <c r="CY119" s="16">
-        <v>0.95145768827025901</v>
+        <v>0.95455792120483962</v>
       </c>
       <c r="CZ119" s="16">
-        <v>1.632318783918965</v>
+        <v>1.632648476098757</v>
       </c>
       <c r="DA119" s="16">
-        <v>1.8371637576540221</v>
+        <v>1.8181053709434614</v>
       </c>
       <c r="DB119" s="11"/>
       <c r="DC119" s="11"/>
@@ -19454,7 +19456,7 @@
     </row>
     <row r="128" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A128" s="6" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="130" spans="1:179" x14ac:dyDescent="0.2">
@@ -19464,7 +19466,7 @@
     </row>
     <row r="131" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A131" s="6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="132" spans="1:179" x14ac:dyDescent="0.2">
@@ -20253,19 +20255,19 @@
         <v>84.969018525096814</v>
       </c>
       <c r="CW137" s="16">
-        <v>79.351306270685953</v>
+        <v>79.429415152339402</v>
       </c>
       <c r="CX137" s="16">
-        <v>79.444404618128374</v>
+        <v>79.437284514487189</v>
       </c>
       <c r="CY137" s="16">
-        <v>81.310465939008012</v>
+        <v>81.323749948322344</v>
       </c>
       <c r="CZ137" s="16">
-        <v>84.54401980801515</v>
+        <v>84.540511607392659</v>
       </c>
       <c r="DA137" s="16">
-        <v>78.638377753934407</v>
+        <v>78.93568984683634</v>
       </c>
       <c r="DB137" s="11"/>
       <c r="DC137" s="11"/>
@@ -20644,19 +20646,19 @@
         <v>1.2290164372884482</v>
       </c>
       <c r="CW138" s="16">
-        <v>1.7856682321627533</v>
+        <v>1.7822719219293908</v>
       </c>
       <c r="CX138" s="16">
-        <v>2.0326698118926685</v>
+        <v>2.0325241173622164</v>
       </c>
       <c r="CY138" s="16">
-        <v>1.7759167334610586</v>
+        <v>1.7762068719340871</v>
       </c>
       <c r="CZ138" s="16">
-        <v>1.14056343091513</v>
+        <v>1.1408087846795998</v>
       </c>
       <c r="DA138" s="16">
-        <v>1.7562114561061812</v>
+        <v>1.7107349373218173</v>
       </c>
       <c r="DB138" s="11"/>
       <c r="DC138" s="11"/>
@@ -21035,19 +21037,19 @@
         <v>12.667540696395408</v>
       </c>
       <c r="CW139" s="16">
-        <v>17.201648956213432</v>
+        <v>17.163515078243403</v>
       </c>
       <c r="CX139" s="16">
-        <v>17.125233220256924</v>
+        <v>17.126042508512043</v>
       </c>
       <c r="CY139" s="16">
-        <v>15.65206924002408</v>
+        <v>15.634354818790472</v>
       </c>
       <c r="CZ139" s="16">
-        <v>13.050736517126339</v>
+        <v>13.053727310672564</v>
       </c>
       <c r="DA139" s="16">
-        <v>17.874769755840166</v>
+        <v>17.64157130451159</v>
       </c>
       <c r="DB139" s="11"/>
       <c r="DC139" s="11"/>
@@ -21426,19 +21428,19 @@
         <v>1.1344243412193271</v>
       </c>
       <c r="CW140" s="16">
-        <v>1.6613765409378489</v>
+        <v>1.6247978474877973</v>
       </c>
       <c r="CX140" s="16">
-        <v>1.3976923497220293</v>
+        <v>1.4041488596385547</v>
       </c>
       <c r="CY140" s="16">
-        <v>1.2615480875068361</v>
+        <v>1.2656883609530809</v>
       </c>
       <c r="CZ140" s="16">
-        <v>1.2646802439433704</v>
+        <v>1.2649522972551737</v>
       </c>
       <c r="DA140" s="16">
-        <v>1.7306410341192358</v>
+        <v>1.7120039113302417</v>
       </c>
       <c r="DB140" s="11"/>
       <c r="DC140" s="11"/>

--- a/Data/National Accounts/PSA-11ESWW_2018PSNA_Qrt.xlsx
+++ b/Data/National Accounts/PSA-11ESWW_2018PSNA_Qrt.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="I:\Shared drives\QNAP\NAP Dissemination\As of April 2026\Tables\NAP Q1 2000 to Q4 2025\Qtr\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\Shared drives\QNAP\NAP Dissemination\As of May 2026\Tables\NAP Q1 2000 to Q1 2026\Qtr\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90E28C18-FBDF-4086-90A2-5626A8499ABE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C8C70EB-159B-4B6B-AFFB-A76560DF036D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="794" xr2:uid="{736930C2-BFBB-46C3-AE9E-AECFC8C3145D}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="794" xr2:uid="{736930C2-BFBB-46C3-AE9E-AECFC8C3145D}"/>
   </bookViews>
   <sheets>
     <sheet name="ESWW" sheetId="11" r:id="rId1"/>
@@ -356,7 +356,7 @@
     <definedName name="pet">#REF!</definedName>
     <definedName name="plastic">#REF!</definedName>
     <definedName name="ply">#REF!</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">ESWW!$A$1:$DA$145</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">ESWW!$A$1:$DB$145</definedName>
     <definedName name="_xlnm.Print_Area">#REF!</definedName>
     <definedName name="PRINT_AREA_MI">#REF!</definedName>
     <definedName name="Print_Titles_MI">#REF!,#REF!</definedName>
@@ -530,7 +530,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="860" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="869" uniqueCount="56">
   <si>
     <t>National Accounts of the Philippines</t>
   </si>
@@ -693,10 +693,13 @@
     <t>Table 12.7 Gross Value Added in Electricity, Steam, Water and Waste Management, by Industry</t>
   </si>
   <si>
-    <t>Q1 2000 to Q4 2025</t>
+    <t>As of May 2026</t>
   </si>
   <si>
-    <t>As of April 2026</t>
+    <t>Q1 2000 to Q1 2026</t>
+  </si>
+  <si>
+    <t>2025 - 2026</t>
   </si>
 </sst>
 </file>
@@ -1201,8 +1204,8 @@
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="41.85546875" style="6" customWidth="1"/>
-    <col min="2" max="105" width="13" style="6" customWidth="1"/>
-    <col min="106" max="16384" width="10" style="6"/>
+    <col min="2" max="106" width="13" style="6" customWidth="1"/>
+    <col min="107" max="16384" width="10" style="6"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:179" x14ac:dyDescent="0.2">
@@ -1217,7 +1220,7 @@
     </row>
     <row r="3" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="5" spans="1:179" x14ac:dyDescent="0.2">
@@ -1227,7 +1230,7 @@
     </row>
     <row r="6" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="7" spans="1:179" x14ac:dyDescent="0.2">
@@ -1393,6 +1396,9 @@
       <c r="CY9" s="20"/>
       <c r="CZ9" s="20"/>
       <c r="DA9" s="20"/>
+      <c r="DB9" s="20">
+        <v>2026</v>
+      </c>
     </row>
     <row r="10" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A10" s="8" t="s">
@@ -1709,6 +1715,9 @@
       </c>
       <c r="DA10" s="15" t="s">
         <v>5</v>
+      </c>
+      <c r="DB10" s="15" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="11" spans="1:179" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
@@ -2030,7 +2039,9 @@
       <c r="DA12" s="21">
         <v>151678.73447707252</v>
       </c>
-      <c r="DB12" s="11"/>
+      <c r="DB12" s="21">
+        <v>208062.25336880863</v>
+      </c>
       <c r="DC12" s="11"/>
       <c r="DD12" s="11"/>
       <c r="DE12" s="11"/>
@@ -2421,7 +2432,9 @@
       <c r="DA13" s="21">
         <v>3133.9499880779931</v>
       </c>
-      <c r="DB13" s="11"/>
+      <c r="DB13" s="21">
+        <v>3768.4415505881188</v>
+      </c>
       <c r="DC13" s="11"/>
       <c r="DD13" s="11"/>
       <c r="DE13" s="11"/>
@@ -2812,7 +2825,9 @@
       <c r="DA14" s="21">
         <v>40051.882566551401</v>
       </c>
-      <c r="DB14" s="11"/>
+      <c r="DB14" s="21">
+        <v>40658.37493505211</v>
+      </c>
       <c r="DC14" s="11"/>
       <c r="DD14" s="11"/>
       <c r="DE14" s="11"/>
@@ -3203,7 +3218,9 @@
       <c r="DA15" s="21">
         <v>3608.4485562785258</v>
       </c>
-      <c r="DB15" s="11"/>
+      <c r="DB15" s="21">
+        <v>3039.1453796547016</v>
+      </c>
       <c r="DC15" s="11"/>
       <c r="DD15" s="11"/>
       <c r="DE15" s="11"/>
@@ -3383,7 +3400,7 @@
       <c r="CY16" s="22"/>
       <c r="CZ16" s="22"/>
       <c r="DA16" s="22"/>
-      <c r="DB16" s="11"/>
+      <c r="DB16" s="22"/>
       <c r="DC16" s="11"/>
       <c r="DD16" s="11"/>
       <c r="DE16" s="11"/>
@@ -3774,7 +3791,9 @@
       <c r="DA17" s="23">
         <v>198473.01558798042</v>
       </c>
-      <c r="DB17" s="11"/>
+      <c r="DB17" s="23">
+        <v>255528.21523410355</v>
+      </c>
       <c r="DC17" s="11"/>
       <c r="DD17" s="11"/>
       <c r="DE17" s="11"/>
@@ -3955,6 +3974,7 @@
       <c r="CY18" s="13"/>
       <c r="CZ18" s="13"/>
       <c r="DA18" s="13"/>
+      <c r="DB18" s="13"/>
     </row>
     <row r="19" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A19" s="14" t="s">
@@ -4333,7 +4353,7 @@
     </row>
     <row r="24" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A24" s="6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="26" spans="1:179" x14ac:dyDescent="0.2">
@@ -4343,7 +4363,7 @@
     </row>
     <row r="27" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A27" s="6" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="28" spans="1:179" x14ac:dyDescent="0.2">
@@ -4509,6 +4529,9 @@
       <c r="CY30" s="20"/>
       <c r="CZ30" s="20"/>
       <c r="DA30" s="20"/>
+      <c r="DB30" s="20">
+        <v>2026</v>
+      </c>
     </row>
     <row r="31" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A31" s="8" t="s">
@@ -4825,6 +4848,9 @@
       </c>
       <c r="DA31" s="15" t="s">
         <v>5</v>
+      </c>
+      <c r="DB31" s="15" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="32" spans="1:179" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
@@ -5146,7 +5172,9 @@
       <c r="DA33" s="21">
         <v>140543.05758884398</v>
       </c>
-      <c r="DB33" s="11"/>
+      <c r="DB33" s="21">
+        <v>135999.1830980035</v>
+      </c>
       <c r="DC33" s="11"/>
       <c r="DD33" s="11"/>
       <c r="DE33" s="11"/>
@@ -5537,7 +5565,9 @@
       <c r="DA34" s="21">
         <v>3045.9215505912725</v>
       </c>
-      <c r="DB34" s="11"/>
+      <c r="DB34" s="21">
+        <v>2972.5738114209544</v>
+      </c>
       <c r="DC34" s="11"/>
       <c r="DD34" s="11"/>
       <c r="DE34" s="11"/>
@@ -5928,7 +5958,9 @@
       <c r="DA35" s="21">
         <v>31410.384537318914</v>
       </c>
-      <c r="DB35" s="11"/>
+      <c r="DB35" s="21">
+        <v>30070.909592794047</v>
+      </c>
       <c r="DC35" s="11"/>
       <c r="DD35" s="11"/>
       <c r="DE35" s="11"/>
@@ -6319,7 +6351,9 @@
       <c r="DA36" s="21">
         <v>3048.1809276549402</v>
       </c>
-      <c r="DB36" s="11"/>
+      <c r="DB36" s="21">
+        <v>2517.0363708224168</v>
+      </c>
       <c r="DC36" s="11"/>
       <c r="DD36" s="11"/>
       <c r="DE36" s="11"/>
@@ -6499,7 +6533,7 @@
       <c r="CY37" s="22"/>
       <c r="CZ37" s="22"/>
       <c r="DA37" s="22"/>
-      <c r="DB37" s="11"/>
+      <c r="DB37" s="22"/>
       <c r="DC37" s="11"/>
       <c r="DD37" s="11"/>
       <c r="DE37" s="11"/>
@@ -6890,7 +6924,9 @@
       <c r="DA38" s="23">
         <v>178047.54460440911</v>
       </c>
-      <c r="DB38" s="11"/>
+      <c r="DB38" s="23">
+        <v>171559.70287304092</v>
+      </c>
       <c r="DC38" s="11"/>
       <c r="DD38" s="11"/>
       <c r="DE38" s="11"/>
@@ -7071,6 +7107,7 @@
       <c r="CY39" s="13"/>
       <c r="CZ39" s="13"/>
       <c r="DA39" s="13"/>
+      <c r="DB39" s="13"/>
     </row>
     <row r="40" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A40" s="14" t="s">
@@ -7449,7 +7486,7 @@
     </row>
     <row r="45" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A45" s="6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="47" spans="1:179" x14ac:dyDescent="0.2">
@@ -7463,10 +7500,11 @@
       <c r="CY47" s="9"/>
       <c r="CZ47" s="9"/>
       <c r="DA47" s="9"/>
+      <c r="DB47" s="9"/>
     </row>
     <row r="48" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A48" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="CY48" s="9"/>
       <c r="CZ48" s="9"/>
@@ -7480,12 +7518,14 @@
       <c r="CY49" s="7"/>
       <c r="CZ49" s="7"/>
       <c r="DA49" s="7"/>
+      <c r="DB49" s="7"/>
     </row>
     <row r="50" spans="1:175" x14ac:dyDescent="0.2">
       <c r="CX50" s="7"/>
       <c r="CY50" s="7"/>
       <c r="CZ50" s="7"/>
       <c r="DA50" s="7"/>
+      <c r="DB50" s="7"/>
     </row>
     <row r="51" spans="1:175" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A51" s="17"/>
@@ -7639,10 +7679,13 @@
       <c r="CU51" s="20"/>
       <c r="CV51" s="20"/>
       <c r="CW51" s="20"/>
-      <c r="CX51" s="24"/>
+      <c r="CX51" s="20" t="s">
+        <v>55</v>
+      </c>
       <c r="CY51" s="24"/>
       <c r="CZ51" s="24"/>
       <c r="DA51" s="24"/>
+      <c r="DB51" s="24"/>
     </row>
     <row r="52" spans="1:175" x14ac:dyDescent="0.2">
       <c r="A52" s="8" t="s">
@@ -7948,17 +7991,20 @@
       <c r="CW52" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="CX52" s="25"/>
+      <c r="CX52" s="8" t="s">
+        <v>2</v>
+      </c>
       <c r="CY52" s="25"/>
       <c r="CZ52" s="25"/>
       <c r="DA52" s="25"/>
+      <c r="DB52" s="25"/>
     </row>
     <row r="53" spans="1:175" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="9"/>
-      <c r="CX53" s="7"/>
       <c r="CY53" s="7"/>
       <c r="CZ53" s="7"/>
       <c r="DA53" s="7"/>
+      <c r="DB53" s="7"/>
     </row>
     <row r="54" spans="1:175" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="6" t="s">
@@ -8264,11 +8310,13 @@
       <c r="CW54" s="16">
         <v>2.7069360285305351</v>
       </c>
-      <c r="CX54" s="18"/>
+      <c r="CX54" s="16">
+        <v>8.0090167166163724</v>
+      </c>
       <c r="CY54" s="18"/>
       <c r="CZ54" s="18"/>
       <c r="DA54" s="18"/>
-      <c r="DB54" s="11"/>
+      <c r="DB54" s="18"/>
       <c r="DC54" s="11"/>
       <c r="DD54" s="11"/>
       <c r="DE54" s="11"/>
@@ -8643,11 +8691,13 @@
       <c r="CW55" s="16">
         <v>-12.209845530530856</v>
       </c>
-      <c r="CX55" s="18"/>
+      <c r="CX55" s="16">
+        <v>-17.023142888909376</v>
+      </c>
       <c r="CY55" s="18"/>
       <c r="CZ55" s="18"/>
       <c r="DA55" s="18"/>
-      <c r="DB55" s="11"/>
+      <c r="DB55" s="18"/>
       <c r="DC55" s="11"/>
       <c r="DD55" s="11"/>
       <c r="DE55" s="11"/>
@@ -9022,11 +9072,13 @@
       <c r="CW56" s="16">
         <v>9.4023863387480304</v>
       </c>
-      <c r="CX56" s="18"/>
+      <c r="CX56" s="16">
+        <v>7.1989341294170828</v>
+      </c>
       <c r="CY56" s="18"/>
       <c r="CZ56" s="18"/>
       <c r="DA56" s="18"/>
-      <c r="DB56" s="11"/>
+      <c r="DB56" s="18"/>
       <c r="DC56" s="11"/>
       <c r="DD56" s="11"/>
       <c r="DE56" s="11"/>
@@ -9401,11 +9453,13 @@
       <c r="CW57" s="16">
         <v>7.1687135853525206</v>
       </c>
-      <c r="CX57" s="18"/>
+      <c r="CX57" s="16">
+        <v>6.3062968584984134</v>
+      </c>
       <c r="CY57" s="18"/>
       <c r="CZ57" s="18"/>
       <c r="DA57" s="18"/>
-      <c r="DB57" s="11"/>
+      <c r="DB57" s="18"/>
       <c r="DC57" s="11"/>
       <c r="DD57" s="11"/>
       <c r="DE57" s="11"/>
@@ -9577,11 +9631,11 @@
       <c r="CU58" s="11"/>
       <c r="CV58" s="11"/>
       <c r="CW58" s="11"/>
-      <c r="CX58" s="10"/>
+      <c r="CX58" s="11"/>
       <c r="CY58" s="10"/>
       <c r="CZ58" s="10"/>
       <c r="DA58" s="10"/>
-      <c r="DB58" s="11"/>
+      <c r="DB58" s="10"/>
       <c r="DC58" s="11"/>
       <c r="DD58" s="11"/>
       <c r="DE58" s="11"/>
@@ -9956,11 +10010,13 @@
       <c r="CW59" s="16">
         <v>3.7888469252985999</v>
       </c>
-      <c r="CX59" s="18"/>
+      <c r="CX59" s="16">
+        <v>7.3817011276327946</v>
+      </c>
       <c r="CY59" s="18"/>
       <c r="CZ59" s="18"/>
       <c r="DA59" s="18"/>
-      <c r="DB59" s="11"/>
+      <c r="DB59" s="18"/>
       <c r="DC59" s="11"/>
       <c r="DD59" s="11"/>
       <c r="DE59" s="11"/>
@@ -10133,19 +10189,20 @@
       <c r="CU60" s="13"/>
       <c r="CV60" s="13"/>
       <c r="CW60" s="13"/>
-      <c r="CX60" s="26"/>
+      <c r="CX60" s="13"/>
       <c r="CY60" s="26"/>
       <c r="CZ60" s="26"/>
       <c r="DA60" s="26"/>
+      <c r="DB60" s="26"/>
     </row>
     <row r="61" spans="1:175" x14ac:dyDescent="0.2">
       <c r="A61" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="CX61" s="7"/>
       <c r="CY61" s="7"/>
       <c r="CZ61" s="7"/>
       <c r="DA61" s="7"/>
+      <c r="DB61" s="7"/>
     </row>
     <row r="62" spans="1:175" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B62" s="19"/>
@@ -10248,11 +10305,11 @@
       <c r="CU62" s="19"/>
       <c r="CV62" s="19"/>
       <c r="CW62" s="19"/>
-      <c r="CX62" s="27"/>
+      <c r="CX62" s="19"/>
       <c r="CY62" s="27"/>
       <c r="CZ62" s="27"/>
       <c r="DA62" s="27"/>
-      <c r="DB62" s="11"/>
+      <c r="DB62" s="27"/>
       <c r="DC62" s="11"/>
       <c r="DD62" s="11"/>
       <c r="DE62" s="11"/>
@@ -10424,11 +10481,11 @@
       <c r="CU63" s="11"/>
       <c r="CV63" s="11"/>
       <c r="CW63" s="11"/>
-      <c r="CX63" s="10"/>
+      <c r="CX63" s="11"/>
       <c r="CY63" s="10"/>
       <c r="CZ63" s="10"/>
       <c r="DA63" s="10"/>
-      <c r="DB63" s="11"/>
+      <c r="DB63" s="10"/>
       <c r="DC63" s="11"/>
       <c r="DD63" s="11"/>
       <c r="DE63" s="11"/>
@@ -10503,67 +10560,67 @@
       <c r="A64" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="CX64" s="7"/>
       <c r="CY64" s="7"/>
       <c r="CZ64" s="7"/>
       <c r="DA64" s="7"/>
+      <c r="DB64" s="7"/>
     </row>
     <row r="65" spans="1:175" x14ac:dyDescent="0.2">
       <c r="A65" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="CX65" s="7"/>
       <c r="CY65" s="7"/>
       <c r="CZ65" s="7"/>
       <c r="DA65" s="7"/>
+      <c r="DB65" s="7"/>
     </row>
     <row r="66" spans="1:175" x14ac:dyDescent="0.2">
       <c r="A66" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="CX66" s="7"/>
+        <v>53</v>
+      </c>
       <c r="CY66" s="7"/>
       <c r="CZ66" s="7"/>
       <c r="DA66" s="7"/>
+      <c r="DB66" s="7"/>
     </row>
     <row r="67" spans="1:175" x14ac:dyDescent="0.2">
-      <c r="CX67" s="7"/>
       <c r="CY67" s="7"/>
       <c r="CZ67" s="7"/>
       <c r="DA67" s="7"/>
+      <c r="DB67" s="7"/>
     </row>
     <row r="68" spans="1:175" x14ac:dyDescent="0.2">
       <c r="A68" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="CX68" s="7"/>
       <c r="CY68" s="7"/>
       <c r="CZ68" s="7"/>
       <c r="DA68" s="7"/>
+      <c r="DB68" s="7"/>
     </row>
     <row r="69" spans="1:175" x14ac:dyDescent="0.2">
       <c r="A69" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="CX69" s="7"/>
+        <v>54</v>
+      </c>
       <c r="CY69" s="7"/>
       <c r="CZ69" s="7"/>
       <c r="DA69" s="7"/>
+      <c r="DB69" s="7"/>
     </row>
     <row r="70" spans="1:175" x14ac:dyDescent="0.2">
       <c r="A70" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="CX70" s="7"/>
       <c r="CY70" s="7"/>
       <c r="CZ70" s="7"/>
       <c r="DA70" s="7"/>
+      <c r="DB70" s="7"/>
     </row>
     <row r="71" spans="1:175" x14ac:dyDescent="0.2">
-      <c r="CX71" s="7"/>
       <c r="CY71" s="7"/>
       <c r="CZ71" s="7"/>
       <c r="DA71" s="7"/>
+      <c r="DB71" s="7"/>
     </row>
     <row r="72" spans="1:175" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A72" s="17"/>
@@ -10717,10 +10774,13 @@
       <c r="CU72" s="20"/>
       <c r="CV72" s="20"/>
       <c r="CW72" s="20"/>
-      <c r="CX72" s="24"/>
+      <c r="CX72" s="20" t="s">
+        <v>55</v>
+      </c>
       <c r="CY72" s="24"/>
       <c r="CZ72" s="24"/>
       <c r="DA72" s="24"/>
+      <c r="DB72" s="24"/>
     </row>
     <row r="73" spans="1:175" x14ac:dyDescent="0.2">
       <c r="A73" s="8" t="s">
@@ -11026,17 +11086,20 @@
       <c r="CW73" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="CX73" s="25"/>
+      <c r="CX73" s="8" t="s">
+        <v>2</v>
+      </c>
       <c r="CY73" s="25"/>
       <c r="CZ73" s="25"/>
       <c r="DA73" s="25"/>
+      <c r="DB73" s="25"/>
     </row>
     <row r="74" spans="1:175" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A74" s="9"/>
-      <c r="CX74" s="7"/>
       <c r="CY74" s="7"/>
       <c r="CZ74" s="7"/>
       <c r="DA74" s="7"/>
+      <c r="DB74" s="7"/>
     </row>
     <row r="75" spans="1:175" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A75" s="6" t="s">
@@ -11342,11 +11405,13 @@
       <c r="CW75" s="16">
         <v>0.14920963365277373</v>
       </c>
-      <c r="CX75" s="18"/>
+      <c r="CX75" s="16">
+        <v>0.53921941932317452</v>
+      </c>
       <c r="CY75" s="18"/>
       <c r="CZ75" s="18"/>
       <c r="DA75" s="18"/>
-      <c r="DB75" s="11"/>
+      <c r="DB75" s="18"/>
       <c r="DC75" s="11"/>
       <c r="DD75" s="11"/>
       <c r="DE75" s="11"/>
@@ -11721,11 +11786,13 @@
       <c r="CW76" s="16">
         <v>-3.2693197677477315</v>
       </c>
-      <c r="CX76" s="18"/>
+      <c r="CX76" s="16">
+        <v>-14.114363421950429</v>
+      </c>
       <c r="CY76" s="18"/>
       <c r="CZ76" s="18"/>
       <c r="DA76" s="18"/>
-      <c r="DB76" s="11"/>
+      <c r="DB76" s="18"/>
       <c r="DC76" s="11"/>
       <c r="DD76" s="11"/>
       <c r="DE76" s="11"/>
@@ -12100,11 +12167,13 @@
       <c r="CW77" s="16">
         <v>3.5825291234249761</v>
       </c>
-      <c r="CX77" s="18"/>
+      <c r="CX77" s="16">
+        <v>3.1129344551469558</v>
+      </c>
       <c r="CY77" s="18"/>
       <c r="CZ77" s="18"/>
       <c r="DA77" s="18"/>
-      <c r="DB77" s="11"/>
+      <c r="DB77" s="18"/>
       <c r="DC77" s="11"/>
       <c r="DD77" s="11"/>
       <c r="DE77" s="11"/>
@@ -12479,11 +12548,13 @@
       <c r="CW78" s="16">
         <v>6.184444592497357</v>
       </c>
-      <c r="CX78" s="18"/>
+      <c r="CX78" s="16">
+        <v>5.2688645699826964</v>
+      </c>
       <c r="CY78" s="18"/>
       <c r="CZ78" s="18"/>
       <c r="DA78" s="18"/>
-      <c r="DB78" s="11"/>
+      <c r="DB78" s="18"/>
       <c r="DC78" s="11"/>
       <c r="DD78" s="11"/>
       <c r="DE78" s="11"/>
@@ -12655,11 +12726,11 @@
       <c r="CU79" s="11"/>
       <c r="CV79" s="11"/>
       <c r="CW79" s="11"/>
-      <c r="CX79" s="10"/>
+      <c r="CX79" s="11"/>
       <c r="CY79" s="10"/>
       <c r="CZ79" s="10"/>
       <c r="DA79" s="10"/>
-      <c r="DB79" s="11"/>
+      <c r="DB79" s="10"/>
       <c r="DC79" s="11"/>
       <c r="DD79" s="11"/>
       <c r="DE79" s="11"/>
@@ -13034,11 +13105,13 @@
       <c r="CW80" s="16">
         <v>0.77562082000216037</v>
       </c>
-      <c r="CX80" s="18"/>
+      <c r="CX80" s="16">
+        <v>0.74856860354772436</v>
+      </c>
       <c r="CY80" s="18"/>
       <c r="CZ80" s="18"/>
       <c r="DA80" s="18"/>
-      <c r="DB80" s="11"/>
+      <c r="DB80" s="18"/>
       <c r="DC80" s="11"/>
       <c r="DD80" s="11"/>
       <c r="DE80" s="11"/>
@@ -13211,19 +13284,20 @@
       <c r="CU81" s="13"/>
       <c r="CV81" s="13"/>
       <c r="CW81" s="13"/>
-      <c r="CX81" s="26"/>
+      <c r="CX81" s="13"/>
       <c r="CY81" s="26"/>
       <c r="CZ81" s="26"/>
       <c r="DA81" s="26"/>
+      <c r="DB81" s="26"/>
     </row>
     <row r="82" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A82" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="CX82" s="7"/>
       <c r="CY82" s="7"/>
       <c r="CZ82" s="7"/>
       <c r="DA82" s="7"/>
+      <c r="DB82" s="7"/>
     </row>
     <row r="83" spans="1:179" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B83" s="11"/>
@@ -13330,7 +13404,7 @@
       <c r="CY83" s="10"/>
       <c r="CZ83" s="10"/>
       <c r="DA83" s="10"/>
-      <c r="DB83" s="11"/>
+      <c r="DB83" s="10"/>
       <c r="DC83" s="11"/>
       <c r="DD83" s="11"/>
       <c r="DE83" s="11"/>
@@ -13506,7 +13580,7 @@
       <c r="CY84" s="10"/>
       <c r="CZ84" s="10"/>
       <c r="DA84" s="10"/>
-      <c r="DB84" s="11"/>
+      <c r="DB84" s="10"/>
       <c r="DC84" s="11"/>
       <c r="DD84" s="11"/>
       <c r="DE84" s="11"/>
@@ -13584,7 +13658,7 @@
     </row>
     <row r="86" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A86" s="6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="88" spans="1:179" x14ac:dyDescent="0.2">
@@ -13594,7 +13668,7 @@
     </row>
     <row r="89" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A89" s="6" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="90" spans="1:179" x14ac:dyDescent="0.2">
@@ -13760,6 +13834,9 @@
       <c r="CY92" s="20"/>
       <c r="CZ92" s="20"/>
       <c r="DA92" s="20"/>
+      <c r="DB92" s="20">
+        <v>2026</v>
+      </c>
     </row>
     <row r="93" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A93" s="8" t="s">
@@ -14076,6 +14153,9 @@
       </c>
       <c r="DA93" s="15" t="s">
         <v>5</v>
+      </c>
+      <c r="DB93" s="15" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="94" spans="1:179" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
@@ -14397,7 +14477,9 @@
       <c r="DA95" s="16">
         <v>107.92332049641738</v>
       </c>
-      <c r="DB95" s="11"/>
+      <c r="DB95" s="16">
+        <v>152.98786994836223</v>
+      </c>
       <c r="DC95" s="11"/>
       <c r="DD95" s="11"/>
       <c r="DE95" s="11"/>
@@ -14788,7 +14870,9 @@
       <c r="DA96" s="16">
         <v>102.89004283349428</v>
       </c>
-      <c r="DB96" s="11"/>
+      <c r="DB96" s="16">
+        <v>126.77369140874998</v>
+      </c>
       <c r="DC96" s="11"/>
       <c r="DD96" s="11"/>
       <c r="DE96" s="11"/>
@@ -15179,7 +15263,9 @@
       <c r="DA97" s="16">
         <v>127.51159578758246</v>
       </c>
-      <c r="DB97" s="11"/>
+      <c r="DB97" s="16">
+        <v>135.20833086071715</v>
+      </c>
       <c r="DC97" s="11"/>
       <c r="DD97" s="11"/>
       <c r="DE97" s="11"/>
@@ -15570,7 +15656,9 @@
       <c r="DA98" s="16">
         <v>118.38039282840789</v>
       </c>
-      <c r="DB98" s="11"/>
+      <c r="DB98" s="16">
+        <v>120.74300613549302</v>
+      </c>
       <c r="DC98" s="11"/>
       <c r="DD98" s="11"/>
       <c r="DE98" s="11"/>
@@ -15750,7 +15838,7 @@
       <c r="CY99" s="16"/>
       <c r="CZ99" s="16"/>
       <c r="DA99" s="16"/>
-      <c r="DB99" s="11"/>
+      <c r="DB99" s="16"/>
       <c r="DC99" s="11"/>
       <c r="DD99" s="11"/>
       <c r="DE99" s="11"/>
@@ -16141,7 +16229,9 @@
       <c r="DA100" s="16">
         <v>111.47191949709455</v>
       </c>
-      <c r="DB100" s="11"/>
+      <c r="DB100" s="16">
+        <v>148.94419316125868</v>
+      </c>
       <c r="DC100" s="11"/>
       <c r="DD100" s="11"/>
       <c r="DE100" s="11"/>
@@ -16322,6 +16412,7 @@
       <c r="CY101" s="13"/>
       <c r="CZ101" s="13"/>
       <c r="DA101" s="13"/>
+      <c r="DB101" s="13"/>
     </row>
     <row r="102" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A102" s="14" t="s">
@@ -16340,7 +16431,7 @@
     </row>
     <row r="107" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A107" s="6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="109" spans="1:179" x14ac:dyDescent="0.2">
@@ -16350,7 +16441,7 @@
     </row>
     <row r="110" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A110" s="6" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="111" spans="1:179" x14ac:dyDescent="0.2">
@@ -16516,6 +16607,9 @@
       <c r="CY113" s="20"/>
       <c r="CZ113" s="20"/>
       <c r="DA113" s="20"/>
+      <c r="DB113" s="20">
+        <v>2026</v>
+      </c>
     </row>
     <row r="114" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A114" s="8" t="s">
@@ -16832,6 +16926,9 @@
       </c>
       <c r="DA114" s="15" t="s">
         <v>5</v>
+      </c>
+      <c r="DB114" s="15" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="115" spans="1:179" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
@@ -17153,7 +17250,9 @@
       <c r="DA116" s="16">
         <v>76.422849739911044</v>
       </c>
-      <c r="DB116" s="11"/>
+      <c r="DB116" s="16">
+        <v>81.424375456225548</v>
+      </c>
       <c r="DC116" s="11"/>
       <c r="DD116" s="11"/>
       <c r="DE116" s="11"/>
@@ -17544,7 +17643,9 @@
       <c r="DA117" s="16">
         <v>1.5790307709053553</v>
       </c>
-      <c r="DB117" s="11"/>
+      <c r="DB117" s="16">
+        <v>1.4747653393718736</v>
+      </c>
       <c r="DC117" s="11"/>
       <c r="DD117" s="11"/>
       <c r="DE117" s="11"/>
@@ -17935,7 +18036,9 @@
       <c r="DA118" s="16">
         <v>20.180014118240138</v>
       </c>
-      <c r="DB118" s="11"/>
+      <c r="DB118" s="16">
+        <v>15.911501161545985</v>
+      </c>
       <c r="DC118" s="11"/>
       <c r="DD118" s="11"/>
       <c r="DE118" s="11"/>
@@ -18326,7 +18429,9 @@
       <c r="DA119" s="16">
         <v>1.8181053709434614</v>
       </c>
-      <c r="DB119" s="11"/>
+      <c r="DB119" s="16">
+        <v>1.1893580428565871</v>
+      </c>
       <c r="DC119" s="11"/>
       <c r="DD119" s="11"/>
       <c r="DE119" s="11"/>
@@ -18897,7 +19002,9 @@
       <c r="DA121" s="16">
         <v>100</v>
       </c>
-      <c r="DB121" s="11"/>
+      <c r="DB121" s="16">
+        <v>100</v>
+      </c>
       <c r="DC121" s="11"/>
       <c r="DD121" s="11"/>
       <c r="DE121" s="11"/>
@@ -19078,6 +19185,7 @@
       <c r="CY122" s="13"/>
       <c r="CZ122" s="13"/>
       <c r="DA122" s="13"/>
+      <c r="DB122" s="13"/>
     </row>
     <row r="123" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A123" s="14" t="s">
@@ -19456,7 +19564,7 @@
     </row>
     <row r="128" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A128" s="6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="130" spans="1:179" x14ac:dyDescent="0.2">
@@ -19466,7 +19574,7 @@
     </row>
     <row r="131" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A131" s="6" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="132" spans="1:179" x14ac:dyDescent="0.2">
@@ -19632,6 +19740,9 @@
       <c r="CY134" s="20"/>
       <c r="CZ134" s="20"/>
       <c r="DA134" s="20"/>
+      <c r="DB134" s="20">
+        <v>2026</v>
+      </c>
     </row>
     <row r="135" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A135" s="8" t="s">
@@ -19948,6 +20059,9 @@
       </c>
       <c r="DA135" s="15" t="s">
         <v>5</v>
+      </c>
+      <c r="DB135" s="15" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="136" spans="1:179" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
@@ -20269,7 +20383,9 @@
       <c r="DA137" s="16">
         <v>78.93568984683634</v>
       </c>
-      <c r="DB137" s="11"/>
+      <c r="DB137" s="16">
+        <v>79.272218837221217</v>
+      </c>
       <c r="DC137" s="11"/>
       <c r="DD137" s="11"/>
       <c r="DE137" s="11"/>
@@ -20660,7 +20776,9 @@
       <c r="DA138" s="16">
         <v>1.7107349373218173</v>
       </c>
-      <c r="DB138" s="11"/>
+      <c r="DB138" s="16">
+        <v>1.732676008200331</v>
+      </c>
       <c r="DC138" s="11"/>
       <c r="DD138" s="11"/>
       <c r="DE138" s="11"/>
@@ -21051,7 +21169,9 @@
       <c r="DA139" s="16">
         <v>17.64157130451159</v>
       </c>
-      <c r="DB139" s="11"/>
+      <c r="DB139" s="16">
+        <v>17.527956209534462</v>
+      </c>
       <c r="DC139" s="11"/>
       <c r="DD139" s="11"/>
       <c r="DE139" s="11"/>
@@ -21442,7 +21562,9 @@
       <c r="DA140" s="16">
         <v>1.7120039113302417</v>
       </c>
-      <c r="DB140" s="11"/>
+      <c r="DB140" s="16">
+        <v>1.4671489450439861</v>
+      </c>
       <c r="DC140" s="11"/>
       <c r="DD140" s="11"/>
       <c r="DE140" s="11"/>
@@ -22013,7 +22135,9 @@
       <c r="DA142" s="16">
         <v>100</v>
       </c>
-      <c r="DB142" s="11"/>
+      <c r="DB142" s="16">
+        <v>100</v>
+      </c>
       <c r="DC142" s="11"/>
       <c r="DD142" s="11"/>
       <c r="DE142" s="11"/>
@@ -22194,31 +22318,35 @@
       <c r="CY143" s="13"/>
       <c r="CZ143" s="13"/>
       <c r="DA143" s="13"/>
+      <c r="DB143" s="13"/>
     </row>
     <row r="144" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A144" s="14" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="146" spans="98:105" x14ac:dyDescent="0.2">
+    <row r="146" spans="98:106" x14ac:dyDescent="0.2">
       <c r="CX146" s="7"/>
       <c r="CY146" s="7"/>
       <c r="CZ146" s="7"/>
       <c r="DA146" s="7"/>
+      <c r="DB146" s="7"/>
     </row>
-    <row r="147" spans="98:105" x14ac:dyDescent="0.2">
+    <row r="147" spans="98:106" x14ac:dyDescent="0.2">
       <c r="CX147" s="7"/>
       <c r="CY147" s="7"/>
       <c r="CZ147" s="7"/>
       <c r="DA147" s="7"/>
+      <c r="DB147" s="7"/>
     </row>
-    <row r="148" spans="98:105" x14ac:dyDescent="0.2">
+    <row r="148" spans="98:106" x14ac:dyDescent="0.2">
       <c r="CX148" s="7"/>
       <c r="CY148" s="7"/>
       <c r="CZ148" s="7"/>
       <c r="DA148" s="7"/>
+      <c r="DB148" s="9"/>
     </row>
-    <row r="149" spans="98:105" x14ac:dyDescent="0.2">
+    <row r="149" spans="98:106" x14ac:dyDescent="0.2">
       <c r="CT149" s="9"/>
       <c r="CU149" s="9"/>
       <c r="CV149" s="9"/>
@@ -22228,7 +22356,7 @@
       <c r="CZ149" s="7"/>
       <c r="DA149" s="7"/>
     </row>
-    <row r="150" spans="98:105" x14ac:dyDescent="0.2">
+    <row r="150" spans="98:106" x14ac:dyDescent="0.2">
       <c r="CT150" s="9"/>
       <c r="CU150" s="9"/>
       <c r="CV150" s="9"/>
@@ -22243,9 +22371,9 @@
   <pageSetup paperSize="9" scale="31" orientation="landscape" r:id="rId1"/>
   <headerFooter alignWithMargins="0"/>
   <rowBreaks count="3" manualBreakCount="3">
-    <brk id="42" max="81" man="1"/>
-    <brk id="84" max="81" man="1"/>
-    <brk id="104" max="81" man="1"/>
+    <brk id="42" max="105" man="1"/>
+    <brk id="84" max="105" man="1"/>
+    <brk id="104" max="105" man="1"/>
   </rowBreaks>
 </worksheet>
 </file>
--- a/Data/National Accounts/PSA-11ESWW_2018PSNA_Qrt.xlsx
+++ b/Data/National Accounts/PSA-11ESWW_2018PSNA_Qrt.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\Shared drives\QNAP\NAP Dissemination\As of May 2026\Tables\NAP Q1 2000 to Q1 2026\Qtr\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\Shared drives\QNAP\NAP Dissemination\As of August 2026\Tables\NAP Q1 2000 to Q2 2026\Qtr\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C8C70EB-159B-4B6B-AFFB-A76560DF036D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EE64C2F-166F-459D-B260-6A930790CED4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="794" xr2:uid="{736930C2-BFBB-46C3-AE9E-AECFC8C3145D}"/>
   </bookViews>
@@ -356,7 +356,7 @@
     <definedName name="pet">#REF!</definedName>
     <definedName name="plastic">#REF!</definedName>
     <definedName name="ply">#REF!</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">ESWW!$A$1:$DB$145</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">ESWW!$A$1:$DC$145</definedName>
     <definedName name="_xlnm.Print_Area">#REF!</definedName>
     <definedName name="PRINT_AREA_MI">#REF!</definedName>
     <definedName name="Print_Titles_MI">#REF!,#REF!</definedName>
@@ -530,7 +530,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="869" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="876" uniqueCount="56">
   <si>
     <t>National Accounts of the Philippines</t>
   </si>
@@ -693,13 +693,13 @@
     <t>Table 12.7 Gross Value Added in Electricity, Steam, Water and Waste Management, by Industry</t>
   </si>
   <si>
-    <t>As of May 2026</t>
+    <t>2025 - 2026</t>
   </si>
   <si>
-    <t>Q1 2000 to Q1 2026</t>
+    <t>As of August 2026</t>
   </si>
   <si>
-    <t>2025 - 2026</t>
+    <t>Q1 2000 to Q2 2026</t>
   </si>
 </sst>
 </file>
@@ -1204,8 +1204,8 @@
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="41.85546875" style="6" customWidth="1"/>
-    <col min="2" max="106" width="13" style="6" customWidth="1"/>
-    <col min="107" max="16384" width="10" style="6"/>
+    <col min="2" max="107" width="13" style="6" customWidth="1"/>
+    <col min="108" max="16384" width="10" style="6"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:179" x14ac:dyDescent="0.2">
@@ -1220,7 +1220,7 @@
     </row>
     <row r="3" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="5" spans="1:179" x14ac:dyDescent="0.2">
@@ -1230,7 +1230,7 @@
     </row>
     <row r="6" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="7" spans="1:179" x14ac:dyDescent="0.2">
@@ -1399,6 +1399,7 @@
       <c r="DB9" s="20">
         <v>2026</v>
       </c>
+      <c r="DC9" s="20"/>
     </row>
     <row r="10" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A10" s="8" t="s">
@@ -1718,6 +1719,9 @@
       </c>
       <c r="DB10" s="15" t="s">
         <v>2</v>
+      </c>
+      <c r="DC10" s="15" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="11" spans="1:179" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
@@ -2040,9 +2044,11 @@
         <v>151678.73447707252</v>
       </c>
       <c r="DB12" s="21">
-        <v>208062.25336880863</v>
-      </c>
-      <c r="DC12" s="11"/>
+        <v>206002.85917050589</v>
+      </c>
+      <c r="DC12" s="21">
+        <v>295958.98477628338</v>
+      </c>
       <c r="DD12" s="11"/>
       <c r="DE12" s="11"/>
       <c r="DF12" s="11"/>
@@ -2435,7 +2441,9 @@
       <c r="DB13" s="21">
         <v>3768.4415505881188</v>
       </c>
-      <c r="DC13" s="11"/>
+      <c r="DC13" s="21">
+        <v>3488.6918293088775</v>
+      </c>
       <c r="DD13" s="11"/>
       <c r="DE13" s="11"/>
       <c r="DF13" s="11"/>
@@ -2826,9 +2834,11 @@
         <v>40051.882566551401</v>
       </c>
       <c r="DB14" s="21">
-        <v>40658.37493505211</v>
-      </c>
-      <c r="DC14" s="11"/>
+        <v>40844.583937579984</v>
+      </c>
+      <c r="DC14" s="21">
+        <v>44071.177110611068</v>
+      </c>
       <c r="DD14" s="11"/>
       <c r="DE14" s="11"/>
       <c r="DF14" s="11"/>
@@ -3219,9 +3229,11 @@
         <v>3608.4485562785258</v>
       </c>
       <c r="DB15" s="21">
-        <v>3039.1453796547016</v>
-      </c>
-      <c r="DC15" s="11"/>
+        <v>3036.8757050691856</v>
+      </c>
+      <c r="DC15" s="21">
+        <v>3076.3522982011641</v>
+      </c>
       <c r="DD15" s="11"/>
       <c r="DE15" s="11"/>
       <c r="DF15" s="11"/>
@@ -3401,7 +3413,7 @@
       <c r="CZ16" s="22"/>
       <c r="DA16" s="22"/>
       <c r="DB16" s="22"/>
-      <c r="DC16" s="11"/>
+      <c r="DC16" s="22"/>
       <c r="DD16" s="11"/>
       <c r="DE16" s="11"/>
       <c r="DF16" s="11"/>
@@ -3792,9 +3804,11 @@
         <v>198473.01558798042</v>
       </c>
       <c r="DB17" s="23">
-        <v>255528.21523410355</v>
-      </c>
-      <c r="DC17" s="11"/>
+        <v>253652.7603637432</v>
+      </c>
+      <c r="DC17" s="23">
+        <v>346595.20601440448</v>
+      </c>
       <c r="DD17" s="11"/>
       <c r="DE17" s="11"/>
       <c r="DF17" s="11"/>
@@ -3975,6 +3989,7 @@
       <c r="CZ18" s="13"/>
       <c r="DA18" s="13"/>
       <c r="DB18" s="13"/>
+      <c r="DC18" s="13"/>
     </row>
     <row r="19" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A19" s="14" t="s">
@@ -4353,7 +4368,7 @@
     </row>
     <row r="24" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A24" s="6" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="26" spans="1:179" x14ac:dyDescent="0.2">
@@ -4363,7 +4378,7 @@
     </row>
     <row r="27" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A27" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="28" spans="1:179" x14ac:dyDescent="0.2">
@@ -4532,6 +4547,7 @@
       <c r="DB30" s="20">
         <v>2026</v>
       </c>
+      <c r="DC30" s="20"/>
     </row>
     <row r="31" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A31" s="8" t="s">
@@ -4851,6 +4867,9 @@
       </c>
       <c r="DB31" s="15" t="s">
         <v>2</v>
+      </c>
+      <c r="DC31" s="15" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="32" spans="1:179" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
@@ -5173,9 +5192,11 @@
         <v>140543.05758884398</v>
       </c>
       <c r="DB33" s="21">
-        <v>135999.1830980035</v>
-      </c>
-      <c r="DC33" s="11"/>
+        <v>134647.23628713077</v>
+      </c>
+      <c r="DC33" s="21">
+        <v>160843.65258549125</v>
+      </c>
       <c r="DD33" s="11"/>
       <c r="DE33" s="11"/>
       <c r="DF33" s="11"/>
@@ -5568,7 +5589,9 @@
       <c r="DB34" s="21">
         <v>2972.5738114209544</v>
       </c>
-      <c r="DC34" s="11"/>
+      <c r="DC34" s="21">
+        <v>3127.32195016884</v>
+      </c>
       <c r="DD34" s="11"/>
       <c r="DE34" s="11"/>
       <c r="DF34" s="11"/>
@@ -5959,9 +5982,11 @@
         <v>31410.384537318914</v>
       </c>
       <c r="DB35" s="21">
-        <v>30070.909592794047</v>
-      </c>
-      <c r="DC35" s="11"/>
+        <v>30208.629658815487</v>
+      </c>
+      <c r="DC35" s="21">
+        <v>30538.328076516991</v>
+      </c>
       <c r="DD35" s="11"/>
       <c r="DE35" s="11"/>
       <c r="DF35" s="11"/>
@@ -6352,9 +6377,11 @@
         <v>3048.1809276549402</v>
       </c>
       <c r="DB36" s="21">
-        <v>2517.0363708224168</v>
-      </c>
-      <c r="DC36" s="11"/>
+        <v>2515.1566142566662</v>
+      </c>
+      <c r="DC36" s="21">
+        <v>2482.0800382042053</v>
+      </c>
       <c r="DD36" s="11"/>
       <c r="DE36" s="11"/>
       <c r="DF36" s="11"/>
@@ -6534,7 +6561,7 @@
       <c r="CZ37" s="22"/>
       <c r="DA37" s="22"/>
       <c r="DB37" s="22"/>
-      <c r="DC37" s="11"/>
+      <c r="DC37" s="22"/>
       <c r="DD37" s="11"/>
       <c r="DE37" s="11"/>
       <c r="DF37" s="11"/>
@@ -6925,9 +6952,11 @@
         <v>178047.54460440911</v>
       </c>
       <c r="DB38" s="23">
-        <v>171559.70287304092</v>
-      </c>
-      <c r="DC38" s="11"/>
+        <v>170343.59637162389</v>
+      </c>
+      <c r="DC38" s="23">
+        <v>196991.3826503813</v>
+      </c>
       <c r="DD38" s="11"/>
       <c r="DE38" s="11"/>
       <c r="DF38" s="11"/>
@@ -7108,6 +7137,7 @@
       <c r="CZ39" s="13"/>
       <c r="DA39" s="13"/>
       <c r="DB39" s="13"/>
+      <c r="DC39" s="13"/>
     </row>
     <row r="40" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A40" s="14" t="s">
@@ -7486,7 +7516,7 @@
     </row>
     <row r="45" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A45" s="6" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="47" spans="1:179" x14ac:dyDescent="0.2">
@@ -7501,31 +7531,32 @@
       <c r="CZ47" s="9"/>
       <c r="DA47" s="9"/>
       <c r="DB47" s="9"/>
+      <c r="DC47" s="9"/>
     </row>
     <row r="48" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A48" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="CY48" s="9"/>
       <c r="CZ48" s="9"/>
       <c r="DA48" s="9"/>
+      <c r="DC48" s="9"/>
     </row>
     <row r="49" spans="1:175" x14ac:dyDescent="0.2">
       <c r="A49" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="CX49" s="7"/>
       <c r="CY49" s="7"/>
       <c r="CZ49" s="7"/>
       <c r="DA49" s="7"/>
       <c r="DB49" s="7"/>
+      <c r="DC49" s="7"/>
     </row>
     <row r="50" spans="1:175" x14ac:dyDescent="0.2">
-      <c r="CX50" s="7"/>
-      <c r="CY50" s="7"/>
       <c r="CZ50" s="7"/>
       <c r="DA50" s="7"/>
       <c r="DB50" s="7"/>
+      <c r="DC50" s="7"/>
     </row>
     <row r="51" spans="1:175" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A51" s="17"/>
@@ -7680,12 +7711,13 @@
       <c r="CV51" s="20"/>
       <c r="CW51" s="20"/>
       <c r="CX51" s="20" t="s">
-        <v>55</v>
-      </c>
-      <c r="CY51" s="24"/>
+        <v>53</v>
+      </c>
+      <c r="CY51" s="20"/>
       <c r="CZ51" s="24"/>
       <c r="DA51" s="24"/>
       <c r="DB51" s="24"/>
+      <c r="DC51" s="24"/>
     </row>
     <row r="52" spans="1:175" x14ac:dyDescent="0.2">
       <c r="A52" s="8" t="s">
@@ -7994,17 +8026,20 @@
       <c r="CX52" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="CY52" s="25"/>
+      <c r="CY52" s="8" t="s">
+        <v>3</v>
+      </c>
       <c r="CZ52" s="25"/>
       <c r="DA52" s="25"/>
       <c r="DB52" s="25"/>
+      <c r="DC52" s="25"/>
     </row>
     <row r="53" spans="1:175" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="9"/>
-      <c r="CY53" s="7"/>
       <c r="CZ53" s="7"/>
       <c r="DA53" s="7"/>
       <c r="DB53" s="7"/>
+      <c r="DC53" s="7"/>
     </row>
     <row r="54" spans="1:175" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="6" t="s">
@@ -8311,13 +8346,15 @@
         <v>2.7069360285305351</v>
       </c>
       <c r="CX54" s="16">
-        <v>8.0090167166163724</v>
-      </c>
-      <c r="CY54" s="18"/>
+        <v>6.9399465763622601</v>
+      </c>
+      <c r="CY54" s="16">
+        <v>14.621112914623154</v>
+      </c>
       <c r="CZ54" s="18"/>
       <c r="DA54" s="18"/>
       <c r="DB54" s="18"/>
-      <c r="DC54" s="11"/>
+      <c r="DC54" s="18"/>
       <c r="DD54" s="11"/>
       <c r="DE54" s="11"/>
       <c r="DF54" s="11"/>
@@ -8694,11 +8731,13 @@
       <c r="CX55" s="16">
         <v>-17.023142888909376</v>
       </c>
-      <c r="CY55" s="18"/>
+      <c r="CY55" s="16">
+        <v>-11.515816869088297</v>
+      </c>
       <c r="CZ55" s="18"/>
       <c r="DA55" s="18"/>
       <c r="DB55" s="18"/>
-      <c r="DC55" s="11"/>
+      <c r="DC55" s="18"/>
       <c r="DD55" s="11"/>
       <c r="DE55" s="11"/>
       <c r="DF55" s="11"/>
@@ -9073,13 +9112,15 @@
         <v>9.4023863387480304</v>
       </c>
       <c r="CX56" s="16">
-        <v>7.1989341294170828</v>
-      </c>
-      <c r="CY56" s="18"/>
+        <v>7.6898884931410691</v>
+      </c>
+      <c r="CY56" s="16">
+        <v>8.6978520774718504</v>
+      </c>
       <c r="CZ56" s="18"/>
       <c r="DA56" s="18"/>
       <c r="DB56" s="18"/>
-      <c r="DC56" s="11"/>
+      <c r="DC56" s="18"/>
       <c r="DD56" s="11"/>
       <c r="DE56" s="11"/>
       <c r="DF56" s="11"/>
@@ -9454,13 +9495,15 @@
         <v>7.1687135853525206</v>
       </c>
       <c r="CX57" s="16">
-        <v>6.3062968584984134</v>
-      </c>
-      <c r="CY57" s="18"/>
+        <v>6.2269058883015731</v>
+      </c>
+      <c r="CY57" s="16">
+        <v>5.454433900924883</v>
+      </c>
       <c r="CZ57" s="18"/>
       <c r="DA57" s="18"/>
       <c r="DB57" s="18"/>
-      <c r="DC57" s="11"/>
+      <c r="DC57" s="18"/>
       <c r="DD57" s="11"/>
       <c r="DE57" s="11"/>
       <c r="DF57" s="11"/>
@@ -9632,11 +9675,11 @@
       <c r="CV58" s="11"/>
       <c r="CW58" s="11"/>
       <c r="CX58" s="11"/>
-      <c r="CY58" s="10"/>
+      <c r="CY58" s="11"/>
       <c r="CZ58" s="10"/>
       <c r="DA58" s="10"/>
       <c r="DB58" s="10"/>
-      <c r="DC58" s="11"/>
+      <c r="DC58" s="10"/>
       <c r="DD58" s="11"/>
       <c r="DE58" s="11"/>
       <c r="DF58" s="11"/>
@@ -10011,13 +10054,15 @@
         <v>3.7888469252985999</v>
       </c>
       <c r="CX59" s="16">
-        <v>7.3817011276327946</v>
-      </c>
-      <c r="CY59" s="18"/>
+        <v>6.5935708063573202</v>
+      </c>
+      <c r="CY59" s="16">
+        <v>13.410590935815407</v>
+      </c>
       <c r="CZ59" s="18"/>
       <c r="DA59" s="18"/>
       <c r="DB59" s="18"/>
-      <c r="DC59" s="11"/>
+      <c r="DC59" s="18"/>
       <c r="DD59" s="11"/>
       <c r="DE59" s="11"/>
       <c r="DF59" s="11"/>
@@ -10190,19 +10235,20 @@
       <c r="CV60" s="13"/>
       <c r="CW60" s="13"/>
       <c r="CX60" s="13"/>
-      <c r="CY60" s="26"/>
+      <c r="CY60" s="13"/>
       <c r="CZ60" s="26"/>
       <c r="DA60" s="26"/>
       <c r="DB60" s="26"/>
+      <c r="DC60" s="26"/>
     </row>
     <row r="61" spans="1:175" x14ac:dyDescent="0.2">
       <c r="A61" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="CY61" s="7"/>
       <c r="CZ61" s="7"/>
       <c r="DA61" s="7"/>
       <c r="DB61" s="7"/>
+      <c r="DC61" s="7"/>
     </row>
     <row r="62" spans="1:175" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B62" s="19"/>
@@ -10306,11 +10352,11 @@
       <c r="CV62" s="19"/>
       <c r="CW62" s="19"/>
       <c r="CX62" s="19"/>
-      <c r="CY62" s="27"/>
+      <c r="CY62" s="19"/>
       <c r="CZ62" s="27"/>
       <c r="DA62" s="27"/>
       <c r="DB62" s="27"/>
-      <c r="DC62" s="11"/>
+      <c r="DC62" s="27"/>
       <c r="DD62" s="11"/>
       <c r="DE62" s="11"/>
       <c r="DF62" s="11"/>
@@ -10482,11 +10528,11 @@
       <c r="CV63" s="11"/>
       <c r="CW63" s="11"/>
       <c r="CX63" s="11"/>
-      <c r="CY63" s="10"/>
+      <c r="CY63" s="11"/>
       <c r="CZ63" s="10"/>
       <c r="DA63" s="10"/>
       <c r="DB63" s="10"/>
-      <c r="DC63" s="11"/>
+      <c r="DC63" s="10"/>
       <c r="DD63" s="11"/>
       <c r="DE63" s="11"/>
       <c r="DF63" s="11"/>
@@ -10560,67 +10606,67 @@
       <c r="A64" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="CY64" s="7"/>
       <c r="CZ64" s="7"/>
       <c r="DA64" s="7"/>
       <c r="DB64" s="7"/>
+      <c r="DC64" s="7"/>
     </row>
     <row r="65" spans="1:175" x14ac:dyDescent="0.2">
       <c r="A65" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="CY65" s="7"/>
       <c r="CZ65" s="7"/>
       <c r="DA65" s="7"/>
       <c r="DB65" s="7"/>
+      <c r="DC65" s="7"/>
     </row>
     <row r="66" spans="1:175" x14ac:dyDescent="0.2">
       <c r="A66" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="CY66" s="7"/>
+        <v>54</v>
+      </c>
       <c r="CZ66" s="7"/>
       <c r="DA66" s="7"/>
       <c r="DB66" s="7"/>
+      <c r="DC66" s="7"/>
     </row>
     <row r="67" spans="1:175" x14ac:dyDescent="0.2">
-      <c r="CY67" s="7"/>
       <c r="CZ67" s="7"/>
       <c r="DA67" s="7"/>
       <c r="DB67" s="7"/>
+      <c r="DC67" s="7"/>
     </row>
     <row r="68" spans="1:175" x14ac:dyDescent="0.2">
       <c r="A68" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="CY68" s="7"/>
       <c r="CZ68" s="7"/>
       <c r="DA68" s="7"/>
       <c r="DB68" s="7"/>
+      <c r="DC68" s="7"/>
     </row>
     <row r="69" spans="1:175" x14ac:dyDescent="0.2">
       <c r="A69" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="CY69" s="7"/>
+        <v>55</v>
+      </c>
       <c r="CZ69" s="7"/>
       <c r="DA69" s="7"/>
       <c r="DB69" s="7"/>
+      <c r="DC69" s="7"/>
     </row>
     <row r="70" spans="1:175" x14ac:dyDescent="0.2">
       <c r="A70" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="CY70" s="7"/>
       <c r="CZ70" s="7"/>
       <c r="DA70" s="7"/>
       <c r="DB70" s="7"/>
+      <c r="DC70" s="7"/>
     </row>
     <row r="71" spans="1:175" x14ac:dyDescent="0.2">
-      <c r="CY71" s="7"/>
       <c r="CZ71" s="7"/>
       <c r="DA71" s="7"/>
       <c r="DB71" s="7"/>
+      <c r="DC71" s="7"/>
     </row>
     <row r="72" spans="1:175" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A72" s="17"/>
@@ -10775,12 +10821,13 @@
       <c r="CV72" s="20"/>
       <c r="CW72" s="20"/>
       <c r="CX72" s="20" t="s">
-        <v>55</v>
-      </c>
-      <c r="CY72" s="24"/>
+        <v>53</v>
+      </c>
+      <c r="CY72" s="20"/>
       <c r="CZ72" s="24"/>
       <c r="DA72" s="24"/>
       <c r="DB72" s="24"/>
+      <c r="DC72" s="24"/>
     </row>
     <row r="73" spans="1:175" x14ac:dyDescent="0.2">
       <c r="A73" s="8" t="s">
@@ -11089,17 +11136,20 @@
       <c r="CX73" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="CY73" s="25"/>
+      <c r="CY73" s="8" t="s">
+        <v>3</v>
+      </c>
       <c r="CZ73" s="25"/>
       <c r="DA73" s="25"/>
       <c r="DB73" s="25"/>
+      <c r="DC73" s="25"/>
     </row>
     <row r="74" spans="1:175" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A74" s="9"/>
-      <c r="CY74" s="7"/>
       <c r="CZ74" s="7"/>
       <c r="DA74" s="7"/>
       <c r="DB74" s="7"/>
+      <c r="DC74" s="7"/>
     </row>
     <row r="75" spans="1:175" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A75" s="6" t="s">
@@ -11406,13 +11456,15 @@
         <v>0.14920963365277373</v>
       </c>
       <c r="CX75" s="16">
-        <v>0.53921941932317452</v>
-      </c>
-      <c r="CY75" s="18"/>
+        <v>-0.46022538589774342</v>
+      </c>
+      <c r="CY75" s="16">
+        <v>4.4525617855722004</v>
+      </c>
       <c r="CZ75" s="18"/>
       <c r="DA75" s="18"/>
       <c r="DB75" s="18"/>
-      <c r="DC75" s="11"/>
+      <c r="DC75" s="18"/>
       <c r="DD75" s="11"/>
       <c r="DE75" s="11"/>
       <c r="DF75" s="11"/>
@@ -11789,11 +11841,13 @@
       <c r="CX76" s="16">
         <v>-14.114363421950429</v>
       </c>
-      <c r="CY76" s="18"/>
+      <c r="CY76" s="16">
+        <v>-7.0152746877656256</v>
+      </c>
       <c r="CZ76" s="18"/>
       <c r="DA76" s="18"/>
       <c r="DB76" s="18"/>
-      <c r="DC76" s="11"/>
+      <c r="DC76" s="18"/>
       <c r="DD76" s="11"/>
       <c r="DE76" s="11"/>
       <c r="DF76" s="11"/>
@@ -12168,13 +12222,15 @@
         <v>3.5825291234249761</v>
       </c>
       <c r="CX77" s="16">
-        <v>3.1129344551469558</v>
-      </c>
-      <c r="CY77" s="18"/>
+        <v>3.5851755789814774</v>
+      </c>
+      <c r="CY77" s="16">
+        <v>3.1567991130652331</v>
+      </c>
       <c r="CZ77" s="18"/>
       <c r="DA77" s="18"/>
       <c r="DB77" s="18"/>
-      <c r="DC77" s="11"/>
+      <c r="DC77" s="18"/>
       <c r="DD77" s="11"/>
       <c r="DE77" s="11"/>
       <c r="DF77" s="11"/>
@@ -12549,13 +12605,15 @@
         <v>6.184444592497357</v>
       </c>
       <c r="CX78" s="16">
-        <v>5.2688645699826964</v>
-      </c>
-      <c r="CY78" s="18"/>
+        <v>5.190248368151714</v>
+      </c>
+      <c r="CY78" s="16">
+        <v>3.5670392032663329</v>
+      </c>
       <c r="CZ78" s="18"/>
       <c r="DA78" s="18"/>
       <c r="DB78" s="18"/>
-      <c r="DC78" s="11"/>
+      <c r="DC78" s="18"/>
       <c r="DD78" s="11"/>
       <c r="DE78" s="11"/>
       <c r="DF78" s="11"/>
@@ -12727,11 +12785,11 @@
       <c r="CV79" s="11"/>
       <c r="CW79" s="11"/>
       <c r="CX79" s="11"/>
-      <c r="CY79" s="10"/>
+      <c r="CY79" s="11"/>
       <c r="CZ79" s="10"/>
       <c r="DA79" s="10"/>
       <c r="DB79" s="10"/>
-      <c r="DC79" s="11"/>
+      <c r="DC79" s="10"/>
       <c r="DD79" s="11"/>
       <c r="DE79" s="11"/>
       <c r="DF79" s="11"/>
@@ -13106,13 +13164,15 @@
         <v>0.77562082000216037</v>
       </c>
       <c r="CX80" s="16">
-        <v>0.74856860354772436</v>
-      </c>
-      <c r="CY80" s="18"/>
+        <v>3.4409117168209491E-2</v>
+      </c>
+      <c r="CY80" s="16">
+        <v>4.0350771959835754</v>
+      </c>
       <c r="CZ80" s="18"/>
       <c r="DA80" s="18"/>
       <c r="DB80" s="18"/>
-      <c r="DC80" s="11"/>
+      <c r="DC80" s="18"/>
       <c r="DD80" s="11"/>
       <c r="DE80" s="11"/>
       <c r="DF80" s="11"/>
@@ -13285,19 +13345,20 @@
       <c r="CV81" s="13"/>
       <c r="CW81" s="13"/>
       <c r="CX81" s="13"/>
-      <c r="CY81" s="26"/>
+      <c r="CY81" s="13"/>
       <c r="CZ81" s="26"/>
       <c r="DA81" s="26"/>
       <c r="DB81" s="26"/>
+      <c r="DC81" s="26"/>
     </row>
     <row r="82" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A82" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="CY82" s="7"/>
       <c r="CZ82" s="7"/>
       <c r="DA82" s="7"/>
       <c r="DB82" s="7"/>
+      <c r="DC82" s="7"/>
     </row>
     <row r="83" spans="1:179" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B83" s="11"/>
@@ -13400,12 +13461,12 @@
       <c r="CU83" s="11"/>
       <c r="CV83" s="11"/>
       <c r="CW83" s="11"/>
-      <c r="CX83" s="10"/>
-      <c r="CY83" s="10"/>
+      <c r="CX83" s="11"/>
+      <c r="CY83" s="11"/>
       <c r="CZ83" s="10"/>
       <c r="DA83" s="10"/>
       <c r="DB83" s="10"/>
-      <c r="DC83" s="11"/>
+      <c r="DC83" s="10"/>
       <c r="DD83" s="11"/>
       <c r="DE83" s="11"/>
       <c r="DF83" s="11"/>
@@ -13581,7 +13642,7 @@
       <c r="CZ84" s="10"/>
       <c r="DA84" s="10"/>
       <c r="DB84" s="10"/>
-      <c r="DC84" s="11"/>
+      <c r="DC84" s="10"/>
       <c r="DD84" s="11"/>
       <c r="DE84" s="11"/>
       <c r="DF84" s="11"/>
@@ -13658,7 +13719,7 @@
     </row>
     <row r="86" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A86" s="6" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="88" spans="1:179" x14ac:dyDescent="0.2">
@@ -13668,7 +13729,7 @@
     </row>
     <row r="89" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A89" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="90" spans="1:179" x14ac:dyDescent="0.2">
@@ -13837,6 +13898,7 @@
       <c r="DB92" s="20">
         <v>2026</v>
       </c>
+      <c r="DC92" s="20"/>
     </row>
     <row r="93" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A93" s="8" t="s">
@@ -14156,6 +14218,9 @@
       </c>
       <c r="DB93" s="15" t="s">
         <v>2</v>
+      </c>
+      <c r="DC93" s="15" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="94" spans="1:179" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
@@ -14478,9 +14543,11 @@
         <v>107.92332049641738</v>
       </c>
       <c r="DB95" s="16">
-        <v>152.98786994836223</v>
-      </c>
-      <c r="DC95" s="11"/>
+        <v>152.99449498630005</v>
+      </c>
+      <c r="DC95" s="16">
+        <v>184.00414316565954</v>
+      </c>
       <c r="DD95" s="11"/>
       <c r="DE95" s="11"/>
       <c r="DF95" s="11"/>
@@ -14873,7 +14940,9 @@
       <c r="DB96" s="16">
         <v>126.77369140874998</v>
       </c>
-      <c r="DC96" s="11"/>
+      <c r="DC96" s="16">
+        <v>111.55525030355533</v>
+      </c>
       <c r="DD96" s="11"/>
       <c r="DE96" s="11"/>
       <c r="DF96" s="11"/>
@@ -15264,9 +15333,11 @@
         <v>127.51159578758246</v>
       </c>
       <c r="DB97" s="16">
-        <v>135.20833086071715</v>
-      </c>
-      <c r="DC97" s="11"/>
+        <v>135.20833086071718</v>
+      </c>
+      <c r="DC97" s="16">
+        <v>144.31430889139085</v>
+      </c>
       <c r="DD97" s="11"/>
       <c r="DE97" s="11"/>
       <c r="DF97" s="11"/>
@@ -15657,9 +15728,11 @@
         <v>118.38039282840789</v>
       </c>
       <c r="DB98" s="16">
-        <v>120.74300613549302</v>
-      </c>
-      <c r="DC98" s="11"/>
+        <v>120.74300613549305</v>
+      </c>
+      <c r="DC98" s="16">
+        <v>123.94250994528433</v>
+      </c>
       <c r="DD98" s="11"/>
       <c r="DE98" s="11"/>
       <c r="DF98" s="11"/>
@@ -15839,7 +15912,7 @@
       <c r="CZ99" s="16"/>
       <c r="DA99" s="16"/>
       <c r="DB99" s="16"/>
-      <c r="DC99" s="11"/>
+      <c r="DC99" s="16"/>
       <c r="DD99" s="11"/>
       <c r="DE99" s="11"/>
       <c r="DF99" s="11"/>
@@ -16230,9 +16303,11 @@
         <v>111.47191949709455</v>
       </c>
       <c r="DB100" s="16">
-        <v>148.94419316125868</v>
-      </c>
-      <c r="DC100" s="11"/>
+        <v>148.90654287371677</v>
+      </c>
+      <c r="DC100" s="16">
+        <v>175.94434911375734</v>
+      </c>
       <c r="DD100" s="11"/>
       <c r="DE100" s="11"/>
       <c r="DF100" s="11"/>
@@ -16413,6 +16488,7 @@
       <c r="CZ101" s="13"/>
       <c r="DA101" s="13"/>
       <c r="DB101" s="13"/>
+      <c r="DC101" s="13"/>
     </row>
     <row r="102" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A102" s="14" t="s">
@@ -16431,7 +16507,7 @@
     </row>
     <row r="107" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A107" s="6" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="109" spans="1:179" x14ac:dyDescent="0.2">
@@ -16441,7 +16517,7 @@
     </row>
     <row r="110" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A110" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="111" spans="1:179" x14ac:dyDescent="0.2">
@@ -16610,6 +16686,7 @@
       <c r="DB113" s="20">
         <v>2026</v>
       </c>
+      <c r="DC113" s="20"/>
     </row>
     <row r="114" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A114" s="8" t="s">
@@ -16929,6 +17006,9 @@
       </c>
       <c r="DB114" s="15" t="s">
         <v>2</v>
+      </c>
+      <c r="DC114" s="15" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="115" spans="1:179" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
@@ -17251,9 +17331,11 @@
         <v>76.422849739911044</v>
       </c>
       <c r="DB116" s="16">
-        <v>81.424375456225548</v>
-      </c>
-      <c r="DC116" s="11"/>
+        <v>81.21451502246363</v>
+      </c>
+      <c r="DC116" s="16">
+        <v>85.39038614515151</v>
+      </c>
       <c r="DD116" s="11"/>
       <c r="DE116" s="11"/>
       <c r="DF116" s="11"/>
@@ -17644,9 +17726,11 @@
         <v>1.5790307709053553</v>
       </c>
       <c r="DB117" s="16">
-        <v>1.4747653393718736</v>
-      </c>
-      <c r="DC117" s="11"/>
+        <v>1.4856694424236099</v>
+      </c>
+      <c r="DC117" s="16">
+        <v>1.006560901238746</v>
+      </c>
       <c r="DD117" s="11"/>
       <c r="DE117" s="11"/>
       <c r="DF117" s="11"/>
@@ -18037,9 +18121,11 @@
         <v>20.180014118240138</v>
       </c>
       <c r="DB118" s="16">
-        <v>15.911501161545985</v>
-      </c>
-      <c r="DC118" s="11"/>
+        <v>16.102558426333712</v>
+      </c>
+      <c r="DC118" s="16">
+        <v>12.715460671657262</v>
+      </c>
       <c r="DD118" s="11"/>
       <c r="DE118" s="11"/>
       <c r="DF118" s="11"/>
@@ -18430,9 +18516,11 @@
         <v>1.8181053709434614</v>
       </c>
       <c r="DB119" s="16">
-        <v>1.1893580428565871</v>
-      </c>
-      <c r="DC119" s="11"/>
+        <v>1.1972571087790427</v>
+      </c>
+      <c r="DC119" s="16">
+        <v>0.88759228195248352</v>
+      </c>
       <c r="DD119" s="11"/>
       <c r="DE119" s="11"/>
       <c r="DF119" s="11"/>
@@ -19005,7 +19093,9 @@
       <c r="DB121" s="16">
         <v>100</v>
       </c>
-      <c r="DC121" s="11"/>
+      <c r="DC121" s="16">
+        <v>100</v>
+      </c>
       <c r="DD121" s="11"/>
       <c r="DE121" s="11"/>
       <c r="DF121" s="11"/>
@@ -19186,6 +19276,7 @@
       <c r="CZ122" s="13"/>
       <c r="DA122" s="13"/>
       <c r="DB122" s="13"/>
+      <c r="DC122" s="13"/>
     </row>
     <row r="123" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A123" s="14" t="s">
@@ -19564,7 +19655,7 @@
     </row>
     <row r="128" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A128" s="6" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="130" spans="1:179" x14ac:dyDescent="0.2">
@@ -19574,7 +19665,7 @@
     </row>
     <row r="131" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A131" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="132" spans="1:179" x14ac:dyDescent="0.2">
@@ -19743,6 +19834,7 @@
       <c r="DB134" s="20">
         <v>2026</v>
       </c>
+      <c r="DC134" s="20"/>
     </row>
     <row r="135" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A135" s="8" t="s">
@@ -20062,6 +20154,9 @@
       </c>
       <c r="DB135" s="15" t="s">
         <v>2</v>
+      </c>
+      <c r="DC135" s="15" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="136" spans="1:179" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
@@ -20384,9 +20479,11 @@
         <v>78.93568984683634</v>
       </c>
       <c r="DB137" s="16">
-        <v>79.272218837221217</v>
-      </c>
-      <c r="DC137" s="11"/>
+        <v>79.044495452228531</v>
+      </c>
+      <c r="DC137" s="16">
+        <v>81.650095766348954</v>
+      </c>
       <c r="DD137" s="11"/>
       <c r="DE137" s="11"/>
       <c r="DF137" s="11"/>
@@ -20777,9 +20874,11 @@
         <v>1.7107349373218173</v>
       </c>
       <c r="DB138" s="16">
-        <v>1.732676008200331</v>
-      </c>
-      <c r="DC138" s="11"/>
+        <v>1.7450458219374136</v>
+      </c>
+      <c r="DC138" s="16">
+        <v>1.5875425148516193</v>
+      </c>
       <c r="DD138" s="11"/>
       <c r="DE138" s="11"/>
       <c r="DF138" s="11"/>
@@ -21170,9 +21269,11 @@
         <v>17.64157130451159</v>
       </c>
       <c r="DB139" s="16">
-        <v>17.527956209534462</v>
-      </c>
-      <c r="DC139" s="11"/>
+        <v>17.733939110286208</v>
+      </c>
+      <c r="DC139" s="16">
+        <v>15.502367497321529</v>
+      </c>
       <c r="DD139" s="11"/>
       <c r="DE139" s="11"/>
       <c r="DF139" s="11"/>
@@ -21563,9 +21664,11 @@
         <v>1.7120039113302417</v>
       </c>
       <c r="DB140" s="16">
-        <v>1.4671489450439861</v>
-      </c>
-      <c r="DC140" s="11"/>
+        <v>1.4765196155478404</v>
+      </c>
+      <c r="DC140" s="16">
+        <v>1.2599942214778912</v>
+      </c>
       <c r="DD140" s="11"/>
       <c r="DE140" s="11"/>
       <c r="DF140" s="11"/>
@@ -22138,7 +22241,9 @@
       <c r="DB142" s="16">
         <v>100</v>
       </c>
-      <c r="DC142" s="11"/>
+      <c r="DC142" s="16">
+        <v>100</v>
+      </c>
       <c r="DD142" s="11"/>
       <c r="DE142" s="11"/>
       <c r="DF142" s="11"/>
@@ -22319,51 +22424,31 @@
       <c r="CZ143" s="13"/>
       <c r="DA143" s="13"/>
       <c r="DB143" s="13"/>
+      <c r="DC143" s="13"/>
     </row>
     <row r="144" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A144" s="14" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="146" spans="98:106" x14ac:dyDescent="0.2">
-      <c r="CX146" s="7"/>
-      <c r="CY146" s="7"/>
-      <c r="CZ146" s="7"/>
-      <c r="DA146" s="7"/>
-      <c r="DB146" s="7"/>
+    <row r="146" spans="98:107" x14ac:dyDescent="0.2">
+      <c r="CX146" s="9"/>
+      <c r="CY146" s="9"/>
+      <c r="CZ146" s="9"/>
+      <c r="DA146" s="9"/>
+      <c r="DB146" s="9"/>
+      <c r="DC146" s="9"/>
     </row>
-    <row r="147" spans="98:106" x14ac:dyDescent="0.2">
-      <c r="CX147" s="7"/>
-      <c r="CY147" s="7"/>
-      <c r="CZ147" s="7"/>
-      <c r="DA147" s="7"/>
-      <c r="DB147" s="7"/>
-    </row>
-    <row r="148" spans="98:106" x14ac:dyDescent="0.2">
-      <c r="CX148" s="7"/>
-      <c r="CY148" s="7"/>
-      <c r="CZ148" s="7"/>
-      <c r="DA148" s="7"/>
-      <c r="DB148" s="9"/>
-    </row>
-    <row r="149" spans="98:106" x14ac:dyDescent="0.2">
+    <row r="149" spans="98:107" x14ac:dyDescent="0.2">
       <c r="CT149" s="9"/>
       <c r="CU149" s="9"/>
       <c r="CV149" s="9"/>
       <c r="CW149" s="7"/>
-      <c r="CX149" s="7"/>
-      <c r="CY149" s="7"/>
-      <c r="CZ149" s="7"/>
-      <c r="DA149" s="7"/>
     </row>
-    <row r="150" spans="98:106" x14ac:dyDescent="0.2">
+    <row r="150" spans="98:107" x14ac:dyDescent="0.2">
       <c r="CT150" s="9"/>
       <c r="CU150" s="9"/>
       <c r="CV150" s="9"/>
-      <c r="CX150" s="9"/>
-      <c r="CY150" s="9"/>
-      <c r="CZ150" s="9"/>
-      <c r="DA150" s="9"/>
     </row>
   </sheetData>
   <printOptions horizontalCentered="1"/>
@@ -22371,9 +22456,9 @@
   <pageSetup paperSize="9" scale="31" orientation="landscape" r:id="rId1"/>
   <headerFooter alignWithMargins="0"/>
   <rowBreaks count="3" manualBreakCount="3">
-    <brk id="42" max="105" man="1"/>
-    <brk id="84" max="105" man="1"/>
-    <brk id="104" max="105" man="1"/>
+    <brk id="42" max="106" man="1"/>
+    <brk id="84" max="106" man="1"/>
+    <brk id="104" max="106" man="1"/>
   </rowBreaks>
 </worksheet>
 </file>